--- a/Outcome/Publish/npjDM/fig3_data.xlsx
+++ b/Outcome/Publish/npjDM/fig3_data.xlsx
@@ -696,7 +696,7 @@
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>6.93</v>
+        <v>7.01</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
@@ -719,7 +719,7 @@
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.75</v>
+        <v>-2.91</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -742,7 +742,7 @@
         <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>6.58</v>
+        <v>6.66</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
@@ -788,7 +788,7 @@
         <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>-12.81</v>
+        <v>-12.84</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
@@ -811,7 +811,7 @@
         <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.65</v>
+        <v>-3.66</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
@@ -834,7 +834,7 @@
         <v>17</v>
       </c>
       <c r="E8" t="n">
-        <v>4.48</v>
+        <v>4.53</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
@@ -880,7 +880,7 @@
         <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
@@ -926,7 +926,7 @@
         <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
@@ -972,7 +972,7 @@
         <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
@@ -995,7 +995,7 @@
         <v>17</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.14</v>
+        <v>-2.16</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
@@ -1018,7 +1018,7 @@
         <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="F16" t="s">
         <v>12</v>
@@ -1041,7 +1041,7 @@
         <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.76</v>
+        <v>-4.58</v>
       </c>
       <c r="F17" t="s">
         <v>12</v>
@@ -1064,7 +1064,7 @@
         <v>13</v>
       </c>
       <c r="E18" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="F18" t="s">
         <v>12</v>
@@ -1087,7 +1087,7 @@
         <v>14</v>
       </c>
       <c r="E19" t="n">
-        <v>3.47</v>
+        <v>3.41</v>
       </c>
       <c r="F19" t="s">
         <v>10</v>
@@ -1110,7 +1110,7 @@
         <v>15</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.73</v>
+        <v>-3.75</v>
       </c>
       <c r="F20" t="s">
         <v>12</v>
@@ -1133,7 +1133,7 @@
         <v>16</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.39</v>
+        <v>-0.41</v>
       </c>
       <c r="F21" t="s">
         <v>12</v>
@@ -1156,7 +1156,7 @@
         <v>17</v>
       </c>
       <c r="E22" t="n">
-        <v>0.59</v>
+        <v>0.56</v>
       </c>
       <c r="F22" t="s">
         <v>12</v>
@@ -1179,7 +1179,7 @@
         <v>9</v>
       </c>
       <c r="E23" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="F23" t="s">
         <v>12</v>
@@ -1202,7 +1202,7 @@
         <v>11</v>
       </c>
       <c r="E24" t="n">
-        <v>6.66</v>
+        <v>6.53</v>
       </c>
       <c r="F24" t="s">
         <v>10</v>
@@ -1225,7 +1225,7 @@
         <v>13</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.99</v>
+        <v>-4.97</v>
       </c>
       <c r="F25" t="s">
         <v>12</v>
@@ -1248,7 +1248,7 @@
         <v>14</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.15</v>
+        <v>-1.07</v>
       </c>
       <c r="F26" t="s">
         <v>12</v>
@@ -1271,7 +1271,7 @@
         <v>15</v>
       </c>
       <c r="E27" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="F27" t="s">
         <v>12</v>
@@ -1294,7 +1294,7 @@
         <v>16</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.61</v>
+        <v>-2.66</v>
       </c>
       <c r="F28" t="s">
         <v>12</v>
@@ -1317,7 +1317,7 @@
         <v>17</v>
       </c>
       <c r="E29" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="F29" t="s">
         <v>12</v>
@@ -1340,7 +1340,7 @@
         <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>0.99</v>
+        <v>0.94</v>
       </c>
       <c r="F30" t="s">
         <v>12</v>
@@ -1363,7 +1363,7 @@
         <v>11</v>
       </c>
       <c r="E31" t="n">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="F31" t="s">
         <v>12</v>
@@ -1409,7 +1409,7 @@
         <v>14</v>
       </c>
       <c r="E33" t="n">
-        <v>3.62</v>
+        <v>3.73</v>
       </c>
       <c r="F33" t="s">
         <v>12</v>
@@ -1432,7 +1432,7 @@
         <v>15</v>
       </c>
       <c r="E34" t="n">
-        <v>-11.7</v>
+        <v>-11.8</v>
       </c>
       <c r="F34" t="s">
         <v>12</v>
@@ -1455,7 +1455,7 @@
         <v>16</v>
       </c>
       <c r="E35" t="n">
-        <v>2.93</v>
+        <v>2.86</v>
       </c>
       <c r="F35" t="s">
         <v>12</v>
@@ -1478,7 +1478,7 @@
         <v>17</v>
       </c>
       <c r="E36" t="n">
-        <v>-4.57</v>
+        <v>-4.65</v>
       </c>
       <c r="F36" t="s">
         <v>12</v>
@@ -1501,7 +1501,7 @@
         <v>9</v>
       </c>
       <c r="E37" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="F37" t="s">
         <v>12</v>
@@ -1524,7 +1524,7 @@
         <v>11</v>
       </c>
       <c r="E38" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="F38" t="s">
         <v>12</v>
@@ -1547,7 +1547,7 @@
         <v>13</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.31</v>
+        <v>-1.15</v>
       </c>
       <c r="F39" t="s">
         <v>12</v>
@@ -1570,7 +1570,7 @@
         <v>14</v>
       </c>
       <c r="E40" t="n">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="F40" t="s">
         <v>12</v>
@@ -1593,7 +1593,7 @@
         <v>15</v>
       </c>
       <c r="E41" t="n">
-        <v>-9.5</v>
+        <v>-9.38</v>
       </c>
       <c r="F41" t="s">
         <v>12</v>
@@ -1616,7 +1616,7 @@
         <v>16</v>
       </c>
       <c r="E42" t="n">
-        <v>7.6</v>
+        <v>7.27</v>
       </c>
       <c r="F42" t="s">
         <v>10</v>
@@ -1639,7 +1639,7 @@
         <v>17</v>
       </c>
       <c r="E43" t="n">
-        <v>-1.39</v>
+        <v>-1.24</v>
       </c>
       <c r="F43" t="s">
         <v>12</v>
@@ -1662,7 +1662,7 @@
         <v>9</v>
       </c>
       <c r="E44" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="F44" t="s">
         <v>12</v>
@@ -1685,7 +1685,7 @@
         <v>11</v>
       </c>
       <c r="E45" t="n">
-        <v>-7.94</v>
+        <v>-7.73</v>
       </c>
       <c r="F45" t="s">
         <v>12</v>
@@ -1731,7 +1731,7 @@
         <v>14</v>
       </c>
       <c r="E47" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="F47" t="s">
         <v>12</v>
@@ -1754,7 +1754,7 @@
         <v>15</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.52</v>
+        <v>-0.49</v>
       </c>
       <c r="F48" t="s">
         <v>12</v>
@@ -1777,7 +1777,7 @@
         <v>16</v>
       </c>
       <c r="E49" t="n">
-        <v>-7.31</v>
+        <v>-7.49</v>
       </c>
       <c r="F49" t="s">
         <v>12</v>
@@ -1800,7 +1800,7 @@
         <v>17</v>
       </c>
       <c r="E50" t="n">
-        <v>5.46</v>
+        <v>5.5</v>
       </c>
       <c r="F50" t="s">
         <v>10</v>
@@ -1823,7 +1823,7 @@
         <v>9</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.49</v>
+        <v>-0.59</v>
       </c>
       <c r="F51" t="s">
         <v>12</v>
@@ -1846,7 +1846,7 @@
         <v>11</v>
       </c>
       <c r="E52" t="n">
-        <v>-5.2</v>
+        <v>-4.72</v>
       </c>
       <c r="F52" t="s">
         <v>12</v>
@@ -1869,7 +1869,7 @@
         <v>13</v>
       </c>
       <c r="E53" t="n">
-        <v>-3.94</v>
+        <v>-4.41</v>
       </c>
       <c r="F53" t="s">
         <v>12</v>
@@ -1892,7 +1892,7 @@
         <v>14</v>
       </c>
       <c r="E54" t="n">
-        <v>7.32</v>
+        <v>7.24</v>
       </c>
       <c r="F54" t="s">
         <v>10</v>
@@ -1915,7 +1915,7 @@
         <v>15</v>
       </c>
       <c r="E55" t="n">
-        <v>4.42</v>
+        <v>4.52</v>
       </c>
       <c r="F55" t="s">
         <v>12</v>
@@ -1938,7 +1938,7 @@
         <v>16</v>
       </c>
       <c r="E56" t="n">
-        <v>-4.32</v>
+        <v>-4.29</v>
       </c>
       <c r="F56" t="s">
         <v>12</v>
@@ -1961,7 +1961,7 @@
         <v>17</v>
       </c>
       <c r="E57" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="F57" t="s">
         <v>12</v>
@@ -1984,7 +1984,7 @@
         <v>9</v>
       </c>
       <c r="E58" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="F58" t="s">
         <v>12</v>
@@ -2007,7 +2007,7 @@
         <v>11</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.55</v>
+        <v>-1.62</v>
       </c>
       <c r="F59" t="s">
         <v>12</v>
@@ -2030,7 +2030,7 @@
         <v>13</v>
       </c>
       <c r="E60" t="n">
-        <v>-4.97</v>
+        <v>-4.96</v>
       </c>
       <c r="F60" t="s">
         <v>12</v>
@@ -2076,7 +2076,7 @@
         <v>15</v>
       </c>
       <c r="E62" t="n">
-        <v>-3.5</v>
+        <v>-3.49</v>
       </c>
       <c r="F62" t="s">
         <v>12</v>
@@ -2099,7 +2099,7 @@
         <v>16</v>
       </c>
       <c r="E63" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="F63" t="s">
         <v>12</v>
@@ -2122,7 +2122,7 @@
         <v>17</v>
       </c>
       <c r="E64" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="F64" t="s">
         <v>12</v>
@@ -2145,7 +2145,7 @@
         <v>9</v>
       </c>
       <c r="E65" t="n">
-        <v>-1.06</v>
+        <v>-0.92</v>
       </c>
       <c r="F65" t="s">
         <v>12</v>
@@ -2168,7 +2168,7 @@
         <v>11</v>
       </c>
       <c r="E66" t="n">
-        <v>6.61</v>
+        <v>6.24</v>
       </c>
       <c r="F66" t="s">
         <v>10</v>
@@ -2191,7 +2191,7 @@
         <v>13</v>
       </c>
       <c r="E67" t="n">
-        <v>-6.48</v>
+        <v>-6.33</v>
       </c>
       <c r="F67" t="s">
         <v>12</v>
@@ -2214,7 +2214,7 @@
         <v>14</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="F68" t="s">
         <v>12</v>
@@ -2237,7 +2237,7 @@
         <v>15</v>
       </c>
       <c r="E69" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="F69" t="s">
         <v>12</v>
@@ -2260,7 +2260,7 @@
         <v>16</v>
       </c>
       <c r="E70" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="F70" t="s">
         <v>12</v>
@@ -2283,7 +2283,7 @@
         <v>17</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.62</v>
+        <v>-1.54</v>
       </c>
       <c r="F71" t="s">
         <v>12</v>
@@ -2306,7 +2306,7 @@
         <v>9</v>
       </c>
       <c r="E72" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="F72" t="s">
         <v>12</v>
@@ -2329,7 +2329,7 @@
         <v>11</v>
       </c>
       <c r="E73" t="n">
-        <v>5.98</v>
+        <v>6.45</v>
       </c>
       <c r="F73" t="s">
         <v>10</v>
@@ -2352,7 +2352,7 @@
         <v>13</v>
       </c>
       <c r="E74" t="n">
-        <v>-2.04</v>
+        <v>-2.38</v>
       </c>
       <c r="F74" t="s">
         <v>12</v>
@@ -2375,7 +2375,7 @@
         <v>14</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.14</v>
+        <v>-0.2</v>
       </c>
       <c r="F75" t="s">
         <v>12</v>
@@ -2398,7 +2398,7 @@
         <v>15</v>
       </c>
       <c r="E76" t="n">
-        <v>-11.23</v>
+        <v>-11.1</v>
       </c>
       <c r="F76" t="s">
         <v>12</v>
@@ -2421,7 +2421,7 @@
         <v>16</v>
       </c>
       <c r="E77" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="F77" t="s">
         <v>12</v>
@@ -2444,7 +2444,7 @@
         <v>17</v>
       </c>
       <c r="E78" t="n">
-        <v>4.75</v>
+        <v>4.61</v>
       </c>
       <c r="F78" t="s">
         <v>12</v>
@@ -2467,7 +2467,7 @@
         <v>9</v>
       </c>
       <c r="E79" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="F79" t="s">
         <v>12</v>
@@ -2490,7 +2490,7 @@
         <v>11</v>
       </c>
       <c r="E80" t="n">
-        <v>-15.74</v>
+        <v>-14.29</v>
       </c>
       <c r="F80" t="s">
         <v>12</v>
@@ -2513,7 +2513,7 @@
         <v>13</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.79</v>
+        <v>-1.21</v>
       </c>
       <c r="F81" t="s">
         <v>12</v>
@@ -2536,7 +2536,7 @@
         <v>14</v>
       </c>
       <c r="E82" t="n">
-        <v>6.66</v>
+        <v>6.59</v>
       </c>
       <c r="F82" t="s">
         <v>10</v>
@@ -2559,7 +2559,7 @@
         <v>15</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.2</v>
+        <v>-0.62</v>
       </c>
       <c r="F83" t="s">
         <v>12</v>
@@ -2582,7 +2582,7 @@
         <v>16</v>
       </c>
       <c r="E84" t="n">
-        <v>4.97</v>
+        <v>4.87</v>
       </c>
       <c r="F84" t="s">
         <v>12</v>
@@ -2605,7 +2605,7 @@
         <v>17</v>
       </c>
       <c r="E85" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="F85" t="s">
         <v>12</v>
@@ -2628,7 +2628,7 @@
         <v>9</v>
       </c>
       <c r="E86" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="F86" t="s">
         <v>12</v>
@@ -2651,7 +2651,7 @@
         <v>11</v>
       </c>
       <c r="E87" t="n">
-        <v>-6.1</v>
+        <v>-7.04</v>
       </c>
       <c r="F87" t="s">
         <v>12</v>
@@ -2674,7 +2674,7 @@
         <v>13</v>
       </c>
       <c r="E88" t="n">
-        <v>6.91</v>
+        <v>6.98</v>
       </c>
       <c r="F88" t="s">
         <v>10</v>
@@ -2697,7 +2697,7 @@
         <v>14</v>
       </c>
       <c r="E89" t="n">
-        <v>5.65</v>
+        <v>5.57</v>
       </c>
       <c r="F89" t="s">
         <v>12</v>
@@ -2720,7 +2720,7 @@
         <v>15</v>
       </c>
       <c r="E90" t="n">
-        <v>-8.15</v>
+        <v>-7.86</v>
       </c>
       <c r="F90" t="s">
         <v>12</v>
@@ -2743,7 +2743,7 @@
         <v>16</v>
       </c>
       <c r="E91" t="n">
-        <v>-1.58</v>
+        <v>-1.39</v>
       </c>
       <c r="F91" t="s">
         <v>12</v>
@@ -2766,7 +2766,7 @@
         <v>17</v>
       </c>
       <c r="E92" t="n">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="F92" t="s">
         <v>12</v>
@@ -2789,7 +2789,7 @@
         <v>9</v>
       </c>
       <c r="E93" t="n">
-        <v>2.99</v>
+        <v>2.77</v>
       </c>
       <c r="F93" t="s">
         <v>12</v>
@@ -2812,7 +2812,7 @@
         <v>11</v>
       </c>
       <c r="E94" t="n">
-        <v>-7.66</v>
+        <v>-5.31</v>
       </c>
       <c r="F94" t="s">
         <v>12</v>
@@ -2835,7 +2835,7 @@
         <v>13</v>
       </c>
       <c r="E95" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="F95" t="s">
         <v>12</v>
@@ -2858,7 +2858,7 @@
         <v>14</v>
       </c>
       <c r="E96" t="n">
-        <v>4.86</v>
+        <v>4.39</v>
       </c>
       <c r="F96" t="s">
         <v>10</v>
@@ -2881,7 +2881,7 @@
         <v>15</v>
       </c>
       <c r="E97" t="n">
-        <v>-10.26</v>
+        <v>-11.07</v>
       </c>
       <c r="F97" t="s">
         <v>12</v>
@@ -2904,7 +2904,7 @@
         <v>16</v>
       </c>
       <c r="E98" t="n">
-        <v>3.98</v>
+        <v>3.63</v>
       </c>
       <c r="F98" t="s">
         <v>12</v>
@@ -2927,7 +2927,7 @@
         <v>17</v>
       </c>
       <c r="E99" t="n">
-        <v>2.85</v>
+        <v>2.57</v>
       </c>
       <c r="F99" t="s">
         <v>12</v>
@@ -2973,7 +2973,7 @@
         <v>11</v>
       </c>
       <c r="E101" t="n">
-        <v>-7.99</v>
+        <v>-8.42</v>
       </c>
       <c r="F101" t="s">
         <v>12</v>
@@ -2996,7 +2996,7 @@
         <v>13</v>
       </c>
       <c r="E102" t="n">
-        <v>-3.07</v>
+        <v>-2.71</v>
       </c>
       <c r="F102" t="s">
         <v>12</v>
@@ -3019,7 +3019,7 @@
         <v>14</v>
       </c>
       <c r="E103" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="F103" t="s">
         <v>12</v>
@@ -3042,7 +3042,7 @@
         <v>15</v>
       </c>
       <c r="E104" t="n">
-        <v>-3.15</v>
+        <v>-3.09</v>
       </c>
       <c r="F104" t="s">
         <v>12</v>
@@ -3065,7 +3065,7 @@
         <v>16</v>
       </c>
       <c r="E105" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="F105" t="s">
         <v>12</v>
@@ -3088,7 +3088,7 @@
         <v>17</v>
       </c>
       <c r="E106" t="n">
-        <v>3.58</v>
+        <v>3.48</v>
       </c>
       <c r="F106" t="s">
         <v>12</v>
@@ -3111,7 +3111,7 @@
         <v>9</v>
       </c>
       <c r="E107" t="n">
-        <v>-0.59</v>
+        <v>-0.48</v>
       </c>
       <c r="F107" t="s">
         <v>12</v>
@@ -3134,7 +3134,7 @@
         <v>11</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.83</v>
+        <v>-0.93</v>
       </c>
       <c r="F108" t="s">
         <v>12</v>
@@ -3157,7 +3157,7 @@
         <v>13</v>
       </c>
       <c r="E109" t="n">
-        <v>5.98</v>
+        <v>6.26</v>
       </c>
       <c r="F109" t="s">
         <v>10</v>
@@ -3180,7 +3180,7 @@
         <v>14</v>
       </c>
       <c r="E110" t="n">
-        <v>3.02</v>
+        <v>3.13</v>
       </c>
       <c r="F110" t="s">
         <v>12</v>
@@ -3203,7 +3203,7 @@
         <v>15</v>
       </c>
       <c r="E111" t="n">
-        <v>-15.4</v>
+        <v>-15.89</v>
       </c>
       <c r="F111" t="s">
         <v>12</v>
@@ -3226,7 +3226,7 @@
         <v>16</v>
       </c>
       <c r="E112" t="n">
-        <v>5.24</v>
+        <v>5.28</v>
       </c>
       <c r="F112" t="s">
         <v>12</v>
@@ -3249,7 +3249,7 @@
         <v>17</v>
       </c>
       <c r="E113" t="n">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="F113" t="s">
         <v>12</v>
@@ -3272,7 +3272,7 @@
         <v>9</v>
       </c>
       <c r="E114" t="n">
-        <v>-9.73</v>
+        <v>-9.56</v>
       </c>
       <c r="F114" t="s">
         <v>12</v>
@@ -3295,7 +3295,7 @@
         <v>11</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.51</v>
+        <v>-1.04</v>
       </c>
       <c r="F115" t="s">
         <v>12</v>
@@ -3318,7 +3318,7 @@
         <v>13</v>
       </c>
       <c r="E116" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="F116" t="s">
         <v>12</v>
@@ -3341,7 +3341,7 @@
         <v>14</v>
       </c>
       <c r="E117" t="n">
-        <v>5.14</v>
+        <v>5.22</v>
       </c>
       <c r="F117" t="s">
         <v>10</v>
@@ -3364,7 +3364,7 @@
         <v>15</v>
       </c>
       <c r="E118" t="n">
-        <v>-0.95</v>
+        <v>-0.9</v>
       </c>
       <c r="F118" t="s">
         <v>12</v>
@@ -3387,7 +3387,7 @@
         <v>16</v>
       </c>
       <c r="E119" t="n">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="F119" t="s">
         <v>12</v>
@@ -3410,7 +3410,7 @@
         <v>17</v>
       </c>
       <c r="E120" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="F120" t="s">
         <v>12</v>
@@ -3433,7 +3433,7 @@
         <v>9</v>
       </c>
       <c r="E121" t="n">
-        <v>4.45</v>
+        <v>4.48</v>
       </c>
       <c r="F121" t="s">
         <v>12</v>
@@ -3456,7 +3456,7 @@
         <v>11</v>
       </c>
       <c r="E122" t="n">
-        <v>-13.67</v>
+        <v>-13.31</v>
       </c>
       <c r="F122" t="s">
         <v>12</v>
@@ -3479,7 +3479,7 @@
         <v>13</v>
       </c>
       <c r="E123" t="n">
-        <v>3.85</v>
+        <v>3.53</v>
       </c>
       <c r="F123" t="s">
         <v>12</v>
@@ -3502,7 +3502,7 @@
         <v>14</v>
       </c>
       <c r="E124" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="F124" t="s">
         <v>12</v>
@@ -3525,7 +3525,7 @@
         <v>15</v>
       </c>
       <c r="E125" t="n">
-        <v>-5.64</v>
+        <v>-5.79</v>
       </c>
       <c r="F125" t="s">
         <v>12</v>
@@ -3548,7 +3548,7 @@
         <v>16</v>
       </c>
       <c r="E126" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="F126" t="s">
         <v>12</v>
@@ -3571,7 +3571,7 @@
         <v>17</v>
       </c>
       <c r="E127" t="n">
-        <v>6.28</v>
+        <v>6.39</v>
       </c>
       <c r="F127" t="s">
         <v>10</v>
@@ -3594,7 +3594,7 @@
         <v>9</v>
       </c>
       <c r="E128" t="n">
-        <v>4.63</v>
+        <v>4.92</v>
       </c>
       <c r="F128" t="s">
         <v>12</v>
@@ -3617,7 +3617,7 @@
         <v>11</v>
       </c>
       <c r="E129" t="n">
-        <v>-4.97</v>
+        <v>-5.87</v>
       </c>
       <c r="F129" t="s">
         <v>12</v>
@@ -3640,7 +3640,7 @@
         <v>13</v>
       </c>
       <c r="E130" t="n">
-        <v>5.35</v>
+        <v>5.72</v>
       </c>
       <c r="F130" t="s">
         <v>10</v>
@@ -3663,7 +3663,7 @@
         <v>14</v>
       </c>
       <c r="E131" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="F131" t="s">
         <v>12</v>
@@ -3686,7 +3686,7 @@
         <v>15</v>
       </c>
       <c r="E132" t="n">
-        <v>-6.81</v>
+        <v>-6.87</v>
       </c>
       <c r="F132" t="s">
         <v>12</v>
@@ -3709,7 +3709,7 @@
         <v>16</v>
       </c>
       <c r="E133" t="n">
-        <v>-3.72</v>
+        <v>-3.64</v>
       </c>
       <c r="F133" t="s">
         <v>12</v>
@@ -3732,7 +3732,7 @@
         <v>17</v>
       </c>
       <c r="E134" t="n">
-        <v>3.99</v>
+        <v>4.15</v>
       </c>
       <c r="F134" t="s">
         <v>12</v>
@@ -3755,7 +3755,7 @@
         <v>9</v>
       </c>
       <c r="E135" t="n">
-        <v>3.93</v>
+        <v>3.98</v>
       </c>
       <c r="F135" t="s">
         <v>12</v>
@@ -3778,7 +3778,7 @@
         <v>11</v>
       </c>
       <c r="E136" t="n">
-        <v>-1.27</v>
+        <v>-1.98</v>
       </c>
       <c r="F136" t="s">
         <v>12</v>
@@ -3801,7 +3801,7 @@
         <v>13</v>
       </c>
       <c r="E137" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="F137" t="s">
         <v>12</v>
@@ -3847,7 +3847,7 @@
         <v>15</v>
       </c>
       <c r="E139" t="n">
-        <v>-15.17</v>
+        <v>-14.62</v>
       </c>
       <c r="F139" t="s">
         <v>12</v>
@@ -3870,7 +3870,7 @@
         <v>16</v>
       </c>
       <c r="E140" t="n">
-        <v>3.57</v>
+        <v>3.69</v>
       </c>
       <c r="F140" t="s">
         <v>12</v>
@@ -3893,7 +3893,7 @@
         <v>17</v>
       </c>
       <c r="E141" t="n">
-        <v>5.58</v>
+        <v>5.61</v>
       </c>
       <c r="F141" t="s">
         <v>10</v>
@@ -3910,13 +3910,13 @@
         <v>40</v>
       </c>
       <c r="C142" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D142" t="s">
         <v>9</v>
       </c>
       <c r="E142" t="n">
-        <v>-6.91</v>
+        <v>-6.87</v>
       </c>
       <c r="F142" t="s">
         <v>12</v>
@@ -3933,13 +3933,13 @@
         <v>40</v>
       </c>
       <c r="C143" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D143" t="s">
         <v>11</v>
       </c>
       <c r="E143" t="n">
-        <v>-6.06</v>
+        <v>-6.94</v>
       </c>
       <c r="F143" t="s">
         <v>12</v>
@@ -3956,16 +3956,16 @@
         <v>40</v>
       </c>
       <c r="C144" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D144" t="s">
         <v>13</v>
       </c>
       <c r="E144" t="n">
-        <v>4.66</v>
+        <v>4.93</v>
       </c>
       <c r="F144" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G144" t="n">
         <v>1</v>
@@ -3979,13 +3979,13 @@
         <v>40</v>
       </c>
       <c r="C145" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D145" t="s">
         <v>14</v>
       </c>
       <c r="E145" t="n">
-        <v>3.92</v>
+        <v>4.09</v>
       </c>
       <c r="F145" t="s">
         <v>12</v>
@@ -4002,13 +4002,13 @@
         <v>40</v>
       </c>
       <c r="C146" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D146" t="s">
         <v>15</v>
       </c>
       <c r="E146" t="n">
-        <v>-4.2</v>
+        <v>-4.11</v>
       </c>
       <c r="F146" t="s">
         <v>12</v>
@@ -4025,16 +4025,16 @@
         <v>40</v>
       </c>
       <c r="C147" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D147" t="s">
         <v>16</v>
       </c>
       <c r="E147" t="n">
-        <v>4.82</v>
+        <v>4.91</v>
       </c>
       <c r="F147" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G147" t="n">
         <v>1</v>
@@ -4048,13 +4048,13 @@
         <v>40</v>
       </c>
       <c r="C148" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D148" t="s">
         <v>17</v>
       </c>
       <c r="E148" t="n">
-        <v>3.76</v>
+        <v>3.99</v>
       </c>
       <c r="F148" t="s">
         <v>12</v>
@@ -4077,7 +4077,7 @@
         <v>9</v>
       </c>
       <c r="E149" t="n">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="F149" t="s">
         <v>12</v>
@@ -4100,7 +4100,7 @@
         <v>11</v>
       </c>
       <c r="E150" t="n">
-        <v>-3.93</v>
+        <v>-5.31</v>
       </c>
       <c r="F150" t="s">
         <v>12</v>
@@ -4123,7 +4123,7 @@
         <v>13</v>
       </c>
       <c r="E151" t="n">
-        <v>-6.61</v>
+        <v>-6.22</v>
       </c>
       <c r="F151" t="s">
         <v>12</v>
@@ -4146,7 +4146,7 @@
         <v>14</v>
       </c>
       <c r="E152" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="F152" t="s">
         <v>12</v>
@@ -4169,7 +4169,7 @@
         <v>15</v>
       </c>
       <c r="E153" t="n">
-        <v>-3.98</v>
+        <v>-3.15</v>
       </c>
       <c r="F153" t="s">
         <v>12</v>
@@ -4192,7 +4192,7 @@
         <v>16</v>
       </c>
       <c r="E154" t="n">
-        <v>8.01</v>
+        <v>7.93</v>
       </c>
       <c r="F154" t="s">
         <v>10</v>
@@ -4215,7 +4215,7 @@
         <v>17</v>
       </c>
       <c r="E155" t="n">
-        <v>0.21</v>
+        <v>0.3</v>
       </c>
       <c r="F155" t="s">
         <v>12</v>
@@ -4238,7 +4238,7 @@
         <v>9</v>
       </c>
       <c r="E156" t="n">
-        <v>4.47</v>
+        <v>4.54</v>
       </c>
       <c r="F156" t="s">
         <v>12</v>
@@ -4261,7 +4261,7 @@
         <v>11</v>
       </c>
       <c r="E157" t="n">
-        <v>-6.63</v>
+        <v>-6.95</v>
       </c>
       <c r="F157" t="s">
         <v>12</v>
@@ -4284,7 +4284,7 @@
         <v>13</v>
       </c>
       <c r="E158" t="n">
-        <v>8.12</v>
+        <v>8.2</v>
       </c>
       <c r="F158" t="s">
         <v>10</v>
@@ -4307,7 +4307,7 @@
         <v>14</v>
       </c>
       <c r="E159" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="F159" t="s">
         <v>12</v>
@@ -4353,7 +4353,7 @@
         <v>16</v>
       </c>
       <c r="E161" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="F161" t="s">
         <v>12</v>
@@ -4376,7 +4376,7 @@
         <v>17</v>
       </c>
       <c r="E162" t="n">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="F162" t="s">
         <v>12</v>
@@ -4399,7 +4399,7 @@
         <v>9</v>
       </c>
       <c r="E163" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="F163" t="s">
         <v>12</v>
@@ -4422,7 +4422,7 @@
         <v>11</v>
       </c>
       <c r="E164" t="n">
-        <v>-2.4</v>
+        <v>-2.46</v>
       </c>
       <c r="F164" t="s">
         <v>12</v>
@@ -4445,7 +4445,7 @@
         <v>13</v>
       </c>
       <c r="E165" t="n">
-        <v>0.19</v>
+        <v>0.12</v>
       </c>
       <c r="F165" t="s">
         <v>12</v>
@@ -4468,7 +4468,7 @@
         <v>14</v>
       </c>
       <c r="E166" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="F166" t="s">
         <v>12</v>
@@ -4491,7 +4491,7 @@
         <v>15</v>
       </c>
       <c r="E167" t="n">
-        <v>-9.34</v>
+        <v>-9.24</v>
       </c>
       <c r="F167" t="s">
         <v>12</v>
@@ -4514,7 +4514,7 @@
         <v>16</v>
       </c>
       <c r="E168" t="n">
-        <v>-0.28</v>
+        <v>-0.21</v>
       </c>
       <c r="F168" t="s">
         <v>12</v>
@@ -4537,7 +4537,7 @@
         <v>17</v>
       </c>
       <c r="E169" t="n">
-        <v>6.37</v>
+        <v>6.29</v>
       </c>
       <c r="F169" t="s">
         <v>10</v>
@@ -19993,31 +19993,31 @@
         <v>43831</v>
       </c>
       <c r="B2" t="n">
-        <v>103.142008007965</v>
+        <v>100.666598923567</v>
       </c>
       <c r="C2" t="n">
-        <v>101.597513185194</v>
+        <v>100.289069523661</v>
       </c>
       <c r="D2" t="s">
         <v>27</v>
       </c>
       <c r="E2" t="n">
-        <v>71.9242464014197</v>
+        <v>69.4874426342305</v>
       </c>
       <c r="F2" t="n">
-        <v>54.0845662216064</v>
+        <v>55.2812886872976</v>
       </c>
       <c r="G2" t="n">
-        <v>135.830383176162</v>
+        <v>130.847239683661</v>
       </c>
       <c r="H2" t="n">
-        <v>155.629519536699</v>
+        <v>151.824300510126</v>
       </c>
       <c r="I2" t="n">
         <v>82</v>
       </c>
       <c r="J2" t="n">
-        <v>19.5975131851943</v>
+        <v>18.2890695236613</v>
       </c>
       <c r="K2" t="s">
         <v>55</v>
@@ -20028,31 +20028,31 @@
         <v>43862</v>
       </c>
       <c r="B3" t="n">
-        <v>94.0257394054479</v>
+        <v>96.7418762135356</v>
       </c>
       <c r="C3" t="n">
-        <v>91.8742709084118</v>
+        <v>94.5146919289456</v>
       </c>
       <c r="D3" t="s">
         <v>27</v>
       </c>
       <c r="E3" t="n">
-        <v>58.9273751908996</v>
+        <v>59.6370736296586</v>
       </c>
       <c r="F3" t="n">
-        <v>47.1678401081767</v>
+        <v>48.4416352539779</v>
       </c>
       <c r="G3" t="n">
-        <v>129.270657653326</v>
+        <v>135.406121737482</v>
       </c>
       <c r="H3" t="n">
-        <v>152.712052388469</v>
+        <v>166.409517440532</v>
       </c>
       <c r="I3" t="n">
         <v>59</v>
       </c>
       <c r="J3" t="n">
-        <v>32.8742709084118</v>
+        <v>35.5146919289456</v>
       </c>
       <c r="K3" t="s">
         <v>55</v>
@@ -20063,31 +20063,31 @@
         <v>43891</v>
       </c>
       <c r="B4" t="n">
-        <v>86.5425435946124</v>
+        <v>86.1095837617557</v>
       </c>
       <c r="C4" t="n">
-        <v>84.3153618483463</v>
+        <v>80.3086393427535</v>
       </c>
       <c r="D4" t="s">
         <v>27</v>
       </c>
       <c r="E4" t="n">
-        <v>50.0382941547041</v>
+        <v>51.0776646112217</v>
       </c>
       <c r="F4" t="n">
-        <v>42.5917722676132</v>
+        <v>37.6725800615182</v>
       </c>
       <c r="G4" t="n">
-        <v>128.853790807822</v>
+        <v>126.779741521836</v>
       </c>
       <c r="H4" t="n">
-        <v>153.258673429339</v>
+        <v>157.602681574389</v>
       </c>
       <c r="I4" t="n">
         <v>37</v>
       </c>
       <c r="J4" t="n">
-        <v>47.3153618483463</v>
+        <v>43.3086393427535</v>
       </c>
       <c r="K4" t="s">
         <v>55</v>
@@ -20098,31 +20098,31 @@
         <v>43922</v>
       </c>
       <c r="B5" t="n">
-        <v>66.2898993953181</v>
+        <v>66.8314536108904</v>
       </c>
       <c r="C5" t="n">
-        <v>61.9609772027194</v>
+        <v>63.1137280628198</v>
       </c>
       <c r="D5" t="s">
         <v>27</v>
       </c>
       <c r="E5" t="n">
-        <v>30.866781538629</v>
+        <v>34.6212165354159</v>
       </c>
       <c r="F5" t="n">
-        <v>16.4181346036355</v>
+        <v>23.1429648057822</v>
       </c>
       <c r="G5" t="n">
-        <v>107.076356436504</v>
+        <v>99.9337748924992</v>
       </c>
       <c r="H5" t="n">
-        <v>133.034409397257</v>
+        <v>145.170297496694</v>
       </c>
       <c r="I5" t="n">
         <v>33</v>
       </c>
       <c r="J5" t="n">
-        <v>28.9609772027194</v>
+        <v>30.1137280628198</v>
       </c>
       <c r="K5" t="s">
         <v>55</v>
@@ -20133,31 +20133,31 @@
         <v>43952</v>
       </c>
       <c r="B6" t="n">
-        <v>88.7569055514601</v>
+        <v>89.7473917890047</v>
       </c>
       <c r="C6" t="n">
-        <v>83.7124355416431</v>
+        <v>84.1441904867504</v>
       </c>
       <c r="D6" t="s">
         <v>27</v>
       </c>
       <c r="E6" t="n">
-        <v>44.3085015210776</v>
+        <v>47.5927067322497</v>
       </c>
       <c r="F6" t="n">
-        <v>28.1100397710468</v>
+        <v>33.4644983835991</v>
       </c>
       <c r="G6" t="n">
-        <v>138.354572229435</v>
+        <v>134.328798480269</v>
       </c>
       <c r="H6" t="n">
-        <v>166.738624565679</v>
+        <v>181.300971786804</v>
       </c>
       <c r="I6" t="n">
         <v>41</v>
       </c>
       <c r="J6" t="n">
-        <v>42.7124355416431</v>
+        <v>43.1441904867504</v>
       </c>
       <c r="K6" t="s">
         <v>55</v>
@@ -20168,31 +20168,31 @@
         <v>43983</v>
       </c>
       <c r="B7" t="n">
-        <v>100.891841189895</v>
+        <v>101.73894715845</v>
       </c>
       <c r="C7" t="n">
-        <v>99.0632945312107</v>
+        <v>93.7539860581792</v>
       </c>
       <c r="D7" t="s">
         <v>27</v>
       </c>
       <c r="E7" t="n">
-        <v>53.621561194501</v>
+        <v>55.8087445417226</v>
       </c>
       <c r="F7" t="n">
-        <v>31.202633797248</v>
+        <v>37.5636707437152</v>
       </c>
       <c r="G7" t="n">
-        <v>151.571214156687</v>
+        <v>161.634727621708</v>
       </c>
       <c r="H7" t="n">
-        <v>201.21182233766</v>
+        <v>194.074924373364</v>
       </c>
       <c r="I7" t="n">
         <v>51</v>
       </c>
       <c r="J7" t="n">
-        <v>48.0632945312107</v>
+        <v>42.7539860581792</v>
       </c>
       <c r="K7" t="s">
         <v>55</v>
@@ -20203,31 +20203,31 @@
         <v>44013</v>
       </c>
       <c r="B8" t="n">
-        <v>74.4819248672666</v>
+        <v>76.3862010568517</v>
       </c>
       <c r="C8" t="n">
-        <v>68.6595201335142</v>
+        <v>72.1815933722544</v>
       </c>
       <c r="D8" t="s">
         <v>27</v>
       </c>
       <c r="E8" t="n">
-        <v>28.1135612049713</v>
+        <v>35.0657954104114</v>
       </c>
       <c r="F8" t="n">
-        <v>14.5349739761833</v>
+        <v>19.2924089499052</v>
       </c>
       <c r="G8" t="n">
-        <v>123.198765157506</v>
+        <v>123.563214608897</v>
       </c>
       <c r="H8" t="n">
-        <v>156.567780607732</v>
+        <v>157.568730593736</v>
       </c>
       <c r="I8" t="n">
         <v>50</v>
       </c>
       <c r="J8" t="n">
-        <v>18.6595201335142</v>
+        <v>22.1815933722544</v>
       </c>
       <c r="K8" t="s">
         <v>55</v>
@@ -20238,31 +20238,31 @@
         <v>44044</v>
       </c>
       <c r="B9" t="n">
-        <v>62.4021516413587</v>
+        <v>63.3352134636723</v>
       </c>
       <c r="C9" t="n">
-        <v>56.6969860911199</v>
+        <v>55.2391736487043</v>
       </c>
       <c r="D9" t="s">
         <v>27</v>
       </c>
       <c r="E9" t="n">
-        <v>19.9955963486962</v>
+        <v>22.4951479988973</v>
       </c>
       <c r="F9" t="n">
-        <v>4.62935227972286</v>
+        <v>8.29649061533934</v>
       </c>
       <c r="G9" t="n">
-        <v>107.1918948958</v>
+        <v>111.744960818904</v>
       </c>
       <c r="H9" t="n">
-        <v>140.149319295739</v>
+        <v>152.06377450755</v>
       </c>
       <c r="I9" t="n">
         <v>66</v>
       </c>
       <c r="J9" t="n">
-        <v>-9.3030139088801</v>
+        <v>-10.7608263512957</v>
       </c>
       <c r="K9" t="s">
         <v>54</v>
@@ -20273,34 +20273,34 @@
         <v>44075</v>
       </c>
       <c r="B10" t="n">
-        <v>51.6009058516841</v>
+        <v>52.3800967217096</v>
       </c>
       <c r="C10" t="n">
-        <v>47.6077475431201</v>
+        <v>44.0583713890754</v>
       </c>
       <c r="D10" t="s">
         <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>10.316903232499</v>
+        <v>15.6183534863695</v>
       </c>
       <c r="F10" t="n">
-        <v>2.83806859850208</v>
+        <v>6.71116730335453</v>
       </c>
       <c r="G10" t="n">
-        <v>96.9371781173669</v>
+        <v>99.5907667189208</v>
       </c>
       <c r="H10" t="n">
-        <v>130.629828528473</v>
+        <v>134.208682162575</v>
       </c>
       <c r="I10" t="n">
         <v>45</v>
       </c>
       <c r="J10" t="n">
-        <v>2.60774754312012</v>
+        <v>-0.941628610924639</v>
       </c>
       <c r="K10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
@@ -20308,31 +20308,31 @@
         <v>44105</v>
       </c>
       <c r="B11" t="n">
-        <v>43.8016229921512</v>
+        <v>43.8558166004629</v>
       </c>
       <c r="C11" t="n">
-        <v>38.5193278795987</v>
+        <v>37.2572942581037</v>
       </c>
       <c r="D11" t="s">
         <v>27</v>
       </c>
       <c r="E11" t="n">
-        <v>6.72531727400113</v>
+        <v>9.9607490448456</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0921136833208134</v>
+        <v>1.33443318599007</v>
       </c>
       <c r="G11" t="n">
-        <v>85.3384065834918</v>
+        <v>82.8451360882952</v>
       </c>
       <c r="H11" t="n">
-        <v>127.848971376049</v>
+        <v>124.860123778509</v>
       </c>
       <c r="I11" t="n">
         <v>34</v>
       </c>
       <c r="J11" t="n">
-        <v>4.51932787959869</v>
+        <v>3.25729425810366</v>
       </c>
       <c r="K11" t="s">
         <v>55</v>
@@ -20343,31 +20343,31 @@
         <v>44136</v>
       </c>
       <c r="B12" t="n">
-        <v>45.1115650845244</v>
+        <v>45.8896959612355</v>
       </c>
       <c r="C12" t="n">
-        <v>39.1519271497735</v>
+        <v>39.5120483215681</v>
       </c>
       <c r="D12" t="s">
         <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>6.3592277737366</v>
+        <v>8.78616073441127</v>
       </c>
       <c r="F12" t="n">
-        <v>0.149860247650734</v>
+        <v>0.323708739676595</v>
       </c>
       <c r="G12" t="n">
-        <v>89.7542000340665</v>
+        <v>86.5256598813251</v>
       </c>
       <c r="H12" t="n">
-        <v>137.934178216876</v>
+        <v>128.451884462198</v>
       </c>
       <c r="I12" t="n">
         <v>28</v>
       </c>
       <c r="J12" t="n">
-        <v>11.1519271497735</v>
+        <v>11.5120483215681</v>
       </c>
       <c r="K12" t="s">
         <v>55</v>
@@ -20378,31 +20378,31 @@
         <v>44166</v>
       </c>
       <c r="B13" t="n">
-        <v>43.5466976623482</v>
+        <v>43.3771513742983</v>
       </c>
       <c r="C13" t="n">
-        <v>35.0243813158426</v>
+        <v>38.5077556169106</v>
       </c>
       <c r="D13" t="s">
         <v>27</v>
       </c>
       <c r="E13" t="n">
-        <v>4.57995071092579</v>
+        <v>7.56217754690498</v>
       </c>
       <c r="F13" t="n">
-        <v>0.230111163303546</v>
+        <v>0.0412446460005103</v>
       </c>
       <c r="G13" t="n">
-        <v>87.7768719356632</v>
+        <v>90.0694398366629</v>
       </c>
       <c r="H13" t="n">
-        <v>152.016293678052</v>
+        <v>114.49627077559</v>
       </c>
       <c r="I13" t="n">
         <v>34</v>
       </c>
       <c r="J13" t="n">
-        <v>1.02438131584255</v>
+        <v>4.50775561691064</v>
       </c>
       <c r="K13" t="s">
         <v>55</v>
@@ -20413,31 +20413,31 @@
         <v>44197</v>
       </c>
       <c r="B14" t="n">
-        <v>94.7370331536177</v>
+        <v>94.7213826296309</v>
       </c>
       <c r="C14" t="n">
-        <v>83.7941169174908</v>
+        <v>84.887589086856</v>
       </c>
       <c r="D14" t="s">
         <v>27</v>
       </c>
       <c r="E14" t="n">
-        <v>26.0961587762575</v>
+        <v>31.8935968947676</v>
       </c>
       <c r="F14" t="n">
-        <v>8.22630633507329</v>
+        <v>17.3364496181972</v>
       </c>
       <c r="G14" t="n">
-        <v>174.653572163901</v>
+        <v>162.243555256515</v>
       </c>
       <c r="H14" t="n">
-        <v>263.462031951206</v>
+        <v>221.077062108814</v>
       </c>
       <c r="I14" t="n">
         <v>34</v>
       </c>
       <c r="J14" t="n">
-        <v>49.7941169174908</v>
+        <v>50.887589086856</v>
       </c>
       <c r="K14" t="s">
         <v>55</v>
@@ -20448,31 +20448,31 @@
         <v>44228</v>
       </c>
       <c r="B15" t="n">
-        <v>87.0130509589936</v>
+        <v>87.3373074842749</v>
       </c>
       <c r="C15" t="n">
-        <v>77.7522941967705</v>
+        <v>79.4679370514014</v>
       </c>
       <c r="D15" t="s">
         <v>27</v>
       </c>
       <c r="E15" t="n">
-        <v>23.0676279192944</v>
+        <v>29.4578807666057</v>
       </c>
       <c r="F15" t="n">
-        <v>3.44990950472972</v>
+        <v>9.8805144635104</v>
       </c>
       <c r="G15" t="n">
-        <v>166.052183053413</v>
+        <v>148.612054405791</v>
       </c>
       <c r="H15" t="n">
-        <v>253.069082515684</v>
+        <v>230.218546215372</v>
       </c>
       <c r="I15" t="n">
         <v>35</v>
       </c>
       <c r="J15" t="n">
-        <v>42.7522941967705</v>
+        <v>44.4679370514014</v>
       </c>
       <c r="K15" t="s">
         <v>55</v>
@@ -20483,31 +20483,31 @@
         <v>44256</v>
       </c>
       <c r="B16" t="n">
-        <v>79.5080079865908</v>
+        <v>80.2328983518101</v>
       </c>
       <c r="C16" t="n">
-        <v>69.421624546242</v>
+        <v>70.6977998704573</v>
       </c>
       <c r="D16" t="s">
         <v>27</v>
       </c>
       <c r="E16" t="n">
-        <v>13.8764583458678</v>
+        <v>21.0571342747125</v>
       </c>
       <c r="F16" t="n">
-        <v>1.70482458399181</v>
+        <v>4.76368753352174</v>
       </c>
       <c r="G16" t="n">
-        <v>157.707683451857</v>
+        <v>158.12618678346</v>
       </c>
       <c r="H16" t="n">
-        <v>221.419474864786</v>
+        <v>208.861312801999</v>
       </c>
       <c r="I16" t="n">
         <v>50</v>
       </c>
       <c r="J16" t="n">
-        <v>19.421624546242</v>
+        <v>20.6977998704573</v>
       </c>
       <c r="K16" t="s">
         <v>55</v>
@@ -20518,31 +20518,31 @@
         <v>44287</v>
       </c>
       <c r="B17" t="n">
-        <v>61.8503770702369</v>
+        <v>62.8477444104797</v>
       </c>
       <c r="C17" t="n">
-        <v>52.1197945455125</v>
+        <v>52.3467627488013</v>
       </c>
       <c r="D17" t="s">
         <v>27</v>
       </c>
       <c r="E17" t="n">
-        <v>7.23565819796883</v>
+        <v>12.7041465426686</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0220410354686744</v>
+        <v>2.60020172373513</v>
       </c>
       <c r="G17" t="n">
-        <v>127.884275811524</v>
+        <v>129.542033593943</v>
       </c>
       <c r="H17" t="n">
-        <v>192.982727879725</v>
+        <v>168.20217189723</v>
       </c>
       <c r="I17" t="n">
         <v>34</v>
       </c>
       <c r="J17" t="n">
-        <v>18.1197945455125</v>
+        <v>18.3467627488013</v>
       </c>
       <c r="K17" t="s">
         <v>55</v>
@@ -20553,31 +20553,31 @@
         <v>44317</v>
       </c>
       <c r="B18" t="n">
-        <v>83.1358002434085</v>
+        <v>84.8980094714249</v>
       </c>
       <c r="C18" t="n">
-        <v>69.5624220497271</v>
+        <v>72.7308875540084</v>
       </c>
       <c r="D18" t="s">
         <v>27</v>
       </c>
       <c r="E18" t="n">
-        <v>13.7570082513373</v>
+        <v>17.1312561325979</v>
       </c>
       <c r="F18" t="n">
-        <v>1.75679509762897</v>
+        <v>5.97026602582112</v>
       </c>
       <c r="G18" t="n">
-        <v>171.151349787637</v>
+        <v>167.893225890588</v>
       </c>
       <c r="H18" t="n">
-        <v>265.180800996923</v>
+        <v>237.256645915028</v>
       </c>
       <c r="I18" t="n">
         <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>45.5624220497271</v>
+        <v>48.7308875540084</v>
       </c>
       <c r="K18" t="s">
         <v>55</v>
@@ -20588,31 +20588,31 @@
         <v>44348</v>
       </c>
       <c r="B19" t="n">
-        <v>88.8655347576364</v>
+        <v>93.2223475120822</v>
       </c>
       <c r="C19" t="n">
-        <v>75.5903295315997</v>
+        <v>79.8312120541057</v>
       </c>
       <c r="D19" t="s">
         <v>27</v>
       </c>
       <c r="E19" t="n">
-        <v>19.1402523989489</v>
+        <v>24.4946527915237</v>
       </c>
       <c r="F19" t="n">
-        <v>1.43123155192356</v>
+        <v>5.02703469335316</v>
       </c>
       <c r="G19" t="n">
-        <v>177.844850149436</v>
+        <v>183.526381521328</v>
       </c>
       <c r="H19" t="n">
-        <v>238.938262125025</v>
+        <v>246.048183582551</v>
       </c>
       <c r="I19" t="n">
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>49.5903295315997</v>
+        <v>53.8312120541057</v>
       </c>
       <c r="K19" t="s">
         <v>55</v>
@@ -20623,31 +20623,31 @@
         <v>44378</v>
       </c>
       <c r="B20" t="n">
-        <v>69.3173467232553</v>
+        <v>72.4502740408591</v>
       </c>
       <c r="C20" t="n">
-        <v>54.2824527016389</v>
+        <v>60.4147028683735</v>
       </c>
       <c r="D20" t="s">
         <v>27</v>
       </c>
       <c r="E20" t="n">
-        <v>9.81863851224515</v>
+        <v>12.1253149415341</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01</v>
+        <v>0.415400516144465</v>
       </c>
       <c r="G20" t="n">
-        <v>158.117686548118</v>
+        <v>144.095908445958</v>
       </c>
       <c r="H20" t="n">
-        <v>208.211869285798</v>
+        <v>220.289503921844</v>
       </c>
       <c r="I20" t="n">
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>32.2824527016389</v>
+        <v>38.4147028683735</v>
       </c>
       <c r="K20" t="s">
         <v>55</v>
@@ -20658,31 +20658,31 @@
         <v>44409</v>
       </c>
       <c r="B21" t="n">
-        <v>59.2690661524549</v>
+        <v>61.4424104364035</v>
       </c>
       <c r="C21" t="n">
-        <v>42.9843233684724</v>
+        <v>44.8171625197965</v>
       </c>
       <c r="D21" t="s">
         <v>27</v>
       </c>
       <c r="E21" t="n">
-        <v>2.18936938760982</v>
+        <v>8.46245116959994</v>
       </c>
       <c r="F21" t="n">
-        <v>0.01</v>
+        <v>0.0164650063529436</v>
       </c>
       <c r="G21" t="n">
-        <v>134.184253712006</v>
+        <v>139.767522486499</v>
       </c>
       <c r="H21" t="n">
-        <v>220.124859668217</v>
+        <v>205.457424602727</v>
       </c>
       <c r="I21" t="n">
         <v>15</v>
       </c>
       <c r="J21" t="n">
-        <v>27.9843233684724</v>
+        <v>29.8171625197965</v>
       </c>
       <c r="K21" t="s">
         <v>55</v>
@@ -20693,31 +20693,31 @@
         <v>44440</v>
       </c>
       <c r="B22" t="n">
-        <v>49.5548252979612</v>
+        <v>51.5260958308507</v>
       </c>
       <c r="C22" t="n">
-        <v>34.4081731420249</v>
+        <v>38.4625187828818</v>
       </c>
       <c r="D22" t="s">
         <v>27</v>
       </c>
       <c r="E22" t="n">
-        <v>0.358154346425045</v>
+        <v>0.819626930785189</v>
       </c>
       <c r="F22" t="n">
         <v>0.01</v>
       </c>
       <c r="G22" t="n">
-        <v>114.572012359576</v>
+        <v>115.845503438084</v>
       </c>
       <c r="H22" t="n">
-        <v>188.668800962201</v>
+        <v>175.658684053434</v>
       </c>
       <c r="I22" t="n">
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>16.4081731420249</v>
+        <v>20.4625187828818</v>
       </c>
       <c r="K22" t="s">
         <v>55</v>
@@ -20728,31 +20728,31 @@
         <v>44470</v>
       </c>
       <c r="B23" t="n">
-        <v>41.509867906575</v>
+        <v>45.0821225192802</v>
       </c>
       <c r="C23" t="n">
-        <v>24.7650391633173</v>
+        <v>32.1665849171207</v>
       </c>
       <c r="D23" t="s">
         <v>27</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01</v>
+        <v>0.290943743376903</v>
       </c>
       <c r="F23" t="n">
         <v>0.01</v>
       </c>
       <c r="G23" t="n">
-        <v>100.917119290509</v>
+        <v>114.129736923523</v>
       </c>
       <c r="H23" t="n">
-        <v>179.551895672748</v>
+        <v>164.085309906739</v>
       </c>
       <c r="I23" t="n">
         <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>7.76503916331729</v>
+        <v>15.1665849171207</v>
       </c>
       <c r="K23" t="s">
         <v>55</v>
@@ -20763,31 +20763,31 @@
         <v>44501</v>
       </c>
       <c r="B24" t="n">
-        <v>42.9994511412661</v>
+        <v>45.7407037512889</v>
       </c>
       <c r="C24" t="n">
-        <v>24.1139539216896</v>
+        <v>31.4396051222677</v>
       </c>
       <c r="D24" t="s">
         <v>27</v>
       </c>
       <c r="E24" t="n">
-        <v>0.01</v>
+        <v>0.499403302863925</v>
       </c>
       <c r="F24" t="n">
         <v>0.01</v>
       </c>
       <c r="G24" t="n">
-        <v>111.090110197049</v>
+        <v>107.730605360966</v>
       </c>
       <c r="H24" t="n">
-        <v>181.065354394703</v>
+        <v>201.822046893442</v>
       </c>
       <c r="I24" t="n">
         <v>14</v>
       </c>
       <c r="J24" t="n">
-        <v>10.1139539216896</v>
+        <v>17.4396051222677</v>
       </c>
       <c r="K24" t="s">
         <v>55</v>
@@ -20798,31 +20798,31 @@
         <v>44531</v>
       </c>
       <c r="B25" t="n">
-        <v>42.5571970869608</v>
+        <v>41.8130136582201</v>
       </c>
       <c r="C25" t="n">
-        <v>23.8113805969587</v>
+        <v>28.4595506549474</v>
       </c>
       <c r="D25" t="s">
         <v>27</v>
       </c>
       <c r="E25" t="n">
-        <v>0.01</v>
+        <v>0.488742918949694</v>
       </c>
       <c r="F25" t="n">
         <v>0.01</v>
       </c>
       <c r="G25" t="n">
-        <v>103.126758820758</v>
+        <v>96.2077096166592</v>
       </c>
       <c r="H25" t="n">
-        <v>209.561261070927</v>
+        <v>197.016188908362</v>
       </c>
       <c r="I25" t="n">
         <v>44</v>
       </c>
       <c r="J25" t="n">
-        <v>-20.1886194030413</v>
+        <v>-15.5404493450526</v>
       </c>
       <c r="K25" t="s">
         <v>54</v>
@@ -20833,31 +20833,31 @@
         <v>44562</v>
       </c>
       <c r="B26" t="n">
-        <v>84.6889188243886</v>
+        <v>87.7811243992726</v>
       </c>
       <c r="C26" t="n">
-        <v>64.4278126841453</v>
+        <v>70.0625473633586</v>
       </c>
       <c r="D26" t="s">
         <v>27</v>
       </c>
       <c r="E26" t="n">
-        <v>5.7088288053982</v>
+        <v>13.1914396725432</v>
       </c>
       <c r="F26" t="n">
-        <v>0.01</v>
+        <v>0.364108191083623</v>
       </c>
       <c r="G26" t="n">
-        <v>195.785830205788</v>
+        <v>177.32594931263</v>
       </c>
       <c r="H26" t="n">
-        <v>283.725801547071</v>
+        <v>280.974727813173</v>
       </c>
       <c r="I26" t="n">
         <v>43</v>
       </c>
       <c r="J26" t="n">
-        <v>21.4278126841453</v>
+        <v>27.0625473633586</v>
       </c>
       <c r="K26" t="s">
         <v>55</v>
@@ -20868,31 +20868,31 @@
         <v>44593</v>
       </c>
       <c r="B27" t="n">
-        <v>78.1756209211953</v>
+        <v>82.2804842216928</v>
       </c>
       <c r="C27" t="n">
-        <v>55.2086479941161</v>
+        <v>63.6668702876464</v>
       </c>
       <c r="D27" t="s">
         <v>27</v>
       </c>
       <c r="E27" t="n">
-        <v>2.75836018681891</v>
+        <v>10.8047902925213</v>
       </c>
       <c r="F27" t="n">
         <v>0.01</v>
       </c>
       <c r="G27" t="n">
-        <v>186.901950945627</v>
+        <v>170.566937608227</v>
       </c>
       <c r="H27" t="n">
-        <v>273.123951520598</v>
+        <v>276.405942719504</v>
       </c>
       <c r="I27" t="n">
         <v>33</v>
       </c>
       <c r="J27" t="n">
-        <v>22.2086479941161</v>
+        <v>30.6668702876464</v>
       </c>
       <c r="K27" t="s">
         <v>55</v>
@@ -20903,31 +20903,31 @@
         <v>44621</v>
       </c>
       <c r="B28" t="n">
-        <v>73.6507958959591</v>
+        <v>75.2669296337228</v>
       </c>
       <c r="C28" t="n">
-        <v>52.5837557617939</v>
+        <v>53.8236667331547</v>
       </c>
       <c r="D28" t="s">
         <v>27</v>
       </c>
       <c r="E28" t="n">
-        <v>0.98041556721328</v>
+        <v>7.86531630237946</v>
       </c>
       <c r="F28" t="n">
         <v>0.01</v>
       </c>
       <c r="G28" t="n">
-        <v>192.816336621353</v>
+        <v>172.272007373865</v>
       </c>
       <c r="H28" t="n">
-        <v>264.445947723355</v>
+        <v>291.291887831</v>
       </c>
       <c r="I28" t="n">
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>30.5837557617939</v>
+        <v>31.8236667331547</v>
       </c>
       <c r="K28" t="s">
         <v>55</v>
@@ -20938,31 +20938,31 @@
         <v>44652</v>
       </c>
       <c r="B29" t="n">
-        <v>57.4123237583535</v>
+        <v>61.2745048721686</v>
       </c>
       <c r="C29" t="n">
-        <v>36.1020053441902</v>
+        <v>37.0189056960663</v>
       </c>
       <c r="D29" t="s">
         <v>27</v>
       </c>
       <c r="E29" t="n">
-        <v>0.01</v>
+        <v>1.08400593878128</v>
       </c>
       <c r="F29" t="n">
         <v>0.01</v>
       </c>
       <c r="G29" t="n">
-        <v>149.952329994698</v>
+        <v>155.034554472374</v>
       </c>
       <c r="H29" t="n">
-        <v>215.031778809861</v>
+        <v>262.780507206639</v>
       </c>
       <c r="I29" t="n">
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>13.1020053441902</v>
+        <v>14.0189056960663</v>
       </c>
       <c r="K29" t="s">
         <v>55</v>
@@ -20973,31 +20973,31 @@
         <v>44682</v>
       </c>
       <c r="B30" t="n">
-        <v>76.669221651119</v>
+        <v>80.7718489614587</v>
       </c>
       <c r="C30" t="n">
-        <v>55.2916964912359</v>
+        <v>57.3388657140311</v>
       </c>
       <c r="D30" t="s">
         <v>27</v>
       </c>
       <c r="E30" t="n">
-        <v>2.54075410008753</v>
+        <v>6.89663887561188</v>
       </c>
       <c r="F30" t="n">
         <v>0.01</v>
       </c>
       <c r="G30" t="n">
-        <v>183.704483706119</v>
+        <v>188.232022949671</v>
       </c>
       <c r="H30" t="n">
-        <v>281.093383722566</v>
+        <v>270.567614153684</v>
       </c>
       <c r="I30" t="n">
         <v>28</v>
       </c>
       <c r="J30" t="n">
-        <v>27.2916964912359</v>
+        <v>29.3388657140311</v>
       </c>
       <c r="K30" t="s">
         <v>55</v>
@@ -21008,31 +21008,31 @@
         <v>44713</v>
       </c>
       <c r="B31" t="n">
-        <v>81.7865411921188</v>
+        <v>88.8990243696895</v>
       </c>
       <c r="C31" t="n">
-        <v>59.3144731747386</v>
+        <v>67.6669895899955</v>
       </c>
       <c r="D31" t="s">
         <v>27</v>
       </c>
       <c r="E31" t="n">
-        <v>3.46780058248574</v>
+        <v>8.42033674078291</v>
       </c>
       <c r="F31" t="n">
         <v>0.01</v>
       </c>
       <c r="G31" t="n">
-        <v>194.093943018879</v>
+        <v>202.668127573672</v>
       </c>
       <c r="H31" t="n">
-        <v>261.977775927729</v>
+        <v>293.611754859096</v>
       </c>
       <c r="I31" t="n">
         <v>36</v>
       </c>
       <c r="J31" t="n">
-        <v>23.3144731747386</v>
+        <v>31.6669895899955</v>
       </c>
       <c r="K31" t="s">
         <v>55</v>
@@ -21043,31 +21043,31 @@
         <v>44743</v>
       </c>
       <c r="B32" t="n">
-        <v>64.3579538422962</v>
+        <v>70.5161549974918</v>
       </c>
       <c r="C32" t="n">
-        <v>40.5559046323125</v>
+        <v>47.3590958952213</v>
       </c>
       <c r="D32" t="s">
         <v>27</v>
       </c>
       <c r="E32" t="n">
-        <v>0.512011607052573</v>
+        <v>2.45556400376434</v>
       </c>
       <c r="F32" t="n">
         <v>0.01</v>
       </c>
       <c r="G32" t="n">
-        <v>157.910875950563</v>
+        <v>171.361820928439</v>
       </c>
       <c r="H32" t="n">
-        <v>255.94437423685</v>
+        <v>247.193202764166</v>
       </c>
       <c r="I32" t="n">
         <v>30</v>
       </c>
       <c r="J32" t="n">
-        <v>10.5559046323125</v>
+        <v>17.3590958952213</v>
       </c>
       <c r="K32" t="s">
         <v>55</v>
@@ -21078,31 +21078,31 @@
         <v>44774</v>
       </c>
       <c r="B33" t="n">
-        <v>53.3823299374726</v>
+        <v>60.084656175415</v>
       </c>
       <c r="C33" t="n">
-        <v>30.5747533534102</v>
+        <v>37.4384227526743</v>
       </c>
       <c r="D33" t="s">
         <v>27</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01</v>
+        <v>0.249003029306044</v>
       </c>
       <c r="F33" t="n">
         <v>0.01</v>
       </c>
       <c r="G33" t="n">
-        <v>146.83523051435</v>
+        <v>156.769989311916</v>
       </c>
       <c r="H33" t="n">
-        <v>226.7885490164</v>
+        <v>232.13043661235</v>
       </c>
       <c r="I33" t="n">
         <v>47</v>
       </c>
       <c r="J33" t="n">
-        <v>-16.4252466465898</v>
+        <v>-9.5615772473257</v>
       </c>
       <c r="K33" t="s">
         <v>54</v>
@@ -21113,10 +21113,10 @@
         <v>44805</v>
       </c>
       <c r="B34" t="n">
-        <v>46.9030591926332</v>
+        <v>50.8069390950979</v>
       </c>
       <c r="C34" t="n">
-        <v>20.3682942417419</v>
+        <v>26.7363792476766</v>
       </c>
       <c r="D34" t="s">
         <v>27</v>
@@ -21128,16 +21128,16 @@
         <v>0.01</v>
       </c>
       <c r="G34" t="n">
-        <v>123.223686491321</v>
+        <v>136.096571937879</v>
       </c>
       <c r="H34" t="n">
-        <v>221.277811051911</v>
+        <v>221.985774339562</v>
       </c>
       <c r="I34" t="n">
         <v>42</v>
       </c>
       <c r="J34" t="n">
-        <v>-21.6317057582581</v>
+        <v>-15.2636207523234</v>
       </c>
       <c r="K34" t="s">
         <v>54</v>
@@ -21148,10 +21148,10 @@
         <v>44835</v>
       </c>
       <c r="B35" t="n">
-        <v>38.5390430745255</v>
+        <v>45.0584094692563</v>
       </c>
       <c r="C35" t="n">
-        <v>14.9614245413198</v>
+        <v>22.3543302818159</v>
       </c>
       <c r="D35" t="s">
         <v>27</v>
@@ -21163,16 +21163,16 @@
         <v>0.01</v>
       </c>
       <c r="G35" t="n">
-        <v>110.318245562532</v>
+        <v>132.964814844239</v>
       </c>
       <c r="H35" t="n">
-        <v>168.317718832482</v>
+        <v>195.974116399089</v>
       </c>
       <c r="I35" t="n">
         <v>34</v>
       </c>
       <c r="J35" t="n">
-        <v>-19.0385754586802</v>
+        <v>-11.6456697181841</v>
       </c>
       <c r="K35" t="s">
         <v>54</v>
@@ -21183,10 +21183,10 @@
         <v>44866</v>
       </c>
       <c r="B36" t="n">
-        <v>39.1202247442964</v>
+        <v>45.8317119817955</v>
       </c>
       <c r="C36" t="n">
-        <v>13.7229651841595</v>
+        <v>20.434201053898</v>
       </c>
       <c r="D36" t="s">
         <v>27</v>
@@ -21198,19 +21198,19 @@
         <v>0.01</v>
       </c>
       <c r="G36" t="n">
-        <v>114.528603312547</v>
+        <v>133.032674138258</v>
       </c>
       <c r="H36" t="n">
-        <v>194.401391417762</v>
+        <v>213.097832523002</v>
       </c>
       <c r="I36" t="n">
         <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>-4.27703481584048</v>
+        <v>2.43420105389804</v>
       </c>
       <c r="K36" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37">
@@ -21218,10 +21218,10 @@
         <v>44896</v>
       </c>
       <c r="B37" t="n">
-        <v>38.2579711737945</v>
+        <v>45.193960015961</v>
       </c>
       <c r="C37" t="n">
-        <v>11.4625244578861</v>
+        <v>20.3429166742347</v>
       </c>
       <c r="D37" t="s">
         <v>27</v>
@@ -21233,16 +21233,16 @@
         <v>0.01</v>
       </c>
       <c r="G37" t="n">
-        <v>106.387674456638</v>
+        <v>128.809316395474</v>
       </c>
       <c r="H37" t="n">
-        <v>200.979077916595</v>
+        <v>198.380772294478</v>
       </c>
       <c r="I37" t="n">
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>-9.53747554211395</v>
+        <v>-0.657083325765253</v>
       </c>
       <c r="K37" t="s">
         <v>54</v>
@@ -21253,31 +21253,31 @@
         <v>44927</v>
       </c>
       <c r="B38" t="n">
-        <v>74.4945243103639</v>
+        <v>88.0329963280195</v>
       </c>
       <c r="C38" t="n">
-        <v>40.1854597986874</v>
+        <v>55.3646340372317</v>
       </c>
       <c r="D38" t="s">
         <v>27</v>
       </c>
       <c r="E38" t="n">
-        <v>0.418743638287346</v>
+        <v>0.321744230277498</v>
       </c>
       <c r="F38" t="n">
         <v>0.01</v>
       </c>
       <c r="G38" t="n">
-        <v>198.649106670676</v>
+        <v>209.001328904019</v>
       </c>
       <c r="H38" t="n">
-        <v>294.944771824597</v>
+        <v>311.870393015987</v>
       </c>
       <c r="I38" t="n">
         <v>30</v>
       </c>
       <c r="J38" t="n">
-        <v>10.1854597986874</v>
+        <v>25.3646340372317</v>
       </c>
       <c r="K38" t="s">
         <v>55</v>
@@ -21288,31 +21288,31 @@
         <v>44958</v>
       </c>
       <c r="B39" t="n">
-        <v>67.788243109008</v>
+        <v>84.6369618076756</v>
       </c>
       <c r="C39" t="n">
-        <v>38.9907980058372</v>
+        <v>51.8559019650029</v>
       </c>
       <c r="D39" t="s">
         <v>27</v>
       </c>
       <c r="E39" t="n">
-        <v>0.01</v>
+        <v>0.03272648535418</v>
       </c>
       <c r="F39" t="n">
         <v>0.01</v>
       </c>
       <c r="G39" t="n">
-        <v>178.867881223583</v>
+        <v>208.888947539077</v>
       </c>
       <c r="H39" t="n">
-        <v>285.006086196899</v>
+        <v>325.359854541751</v>
       </c>
       <c r="I39" t="n">
         <v>14</v>
       </c>
       <c r="J39" t="n">
-        <v>24.9907980058372</v>
+        <v>37.8559019650029</v>
       </c>
       <c r="K39" t="s">
         <v>55</v>
@@ -21323,10 +21323,10 @@
         <v>44986</v>
       </c>
       <c r="B40" t="n">
-        <v>63.2493669754588</v>
+        <v>77.6475784401502</v>
       </c>
       <c r="C40" t="n">
-        <v>27.4022355646622</v>
+        <v>43.7060874155232</v>
       </c>
       <c r="D40" t="s">
         <v>27</v>
@@ -21338,16 +21338,16 @@
         <v>0.01</v>
       </c>
       <c r="G40" t="n">
-        <v>173.671929935888</v>
+        <v>189.913219982523</v>
       </c>
       <c r="H40" t="n">
-        <v>274.999330645438</v>
+        <v>300.58238365484</v>
       </c>
       <c r="I40" t="n">
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>7.40223556466217</v>
+        <v>23.7060874155232</v>
       </c>
       <c r="K40" t="s">
         <v>55</v>
@@ -21358,10 +21358,10 @@
         <v>45017</v>
       </c>
       <c r="B41" t="n">
-        <v>51.7031895985752</v>
+        <v>64.0110462147869</v>
       </c>
       <c r="C41" t="n">
-        <v>21.026365975</v>
+        <v>28.7149235139815</v>
       </c>
       <c r="D41" t="s">
         <v>27</v>
@@ -21373,16 +21373,16 @@
         <v>0.01</v>
       </c>
       <c r="G41" t="n">
-        <v>143.267838869884</v>
+        <v>167.180941269807</v>
       </c>
       <c r="H41" t="n">
-        <v>250.527870317272</v>
+        <v>295.258981225053</v>
       </c>
       <c r="I41" t="n">
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>4.02636597499999</v>
+        <v>11.7149235139815</v>
       </c>
       <c r="K41" t="s">
         <v>55</v>
@@ -21393,10 +21393,10 @@
         <v>45047</v>
       </c>
       <c r="B42" t="n">
-        <v>67.1558955882816</v>
+        <v>82.0711229786771</v>
       </c>
       <c r="C42" t="n">
-        <v>35.7744956039816</v>
+        <v>47.336586691389</v>
       </c>
       <c r="D42" t="s">
         <v>27</v>
@@ -21408,16 +21408,16 @@
         <v>0.01</v>
       </c>
       <c r="G42" t="n">
-        <v>183.506824052962</v>
+        <v>208.733769586835</v>
       </c>
       <c r="H42" t="n">
-        <v>278.928158168128</v>
+        <v>352.253552732659</v>
       </c>
       <c r="I42" t="n">
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>7.7744956039816</v>
+        <v>19.336586691389</v>
       </c>
       <c r="K42" t="s">
         <v>55</v>
@@ -21428,10 +21428,10 @@
         <v>45078</v>
       </c>
       <c r="B43" t="n">
-        <v>75.6563967075844</v>
+        <v>92.5003723935378</v>
       </c>
       <c r="C43" t="n">
-        <v>40.2472228335174</v>
+        <v>54.1491909398007</v>
       </c>
       <c r="D43" t="s">
         <v>27</v>
@@ -21443,16 +21443,16 @@
         <v>0.01</v>
       </c>
       <c r="G43" t="n">
-        <v>203.711751316506</v>
+        <v>226.913652377636</v>
       </c>
       <c r="H43" t="n">
-        <v>328.822319509523</v>
+        <v>366.471365390053</v>
       </c>
       <c r="I43" t="n">
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>14.2472228335174</v>
+        <v>28.1491909398007</v>
       </c>
       <c r="K43" t="s">
         <v>55</v>
@@ -21463,10 +21463,10 @@
         <v>45108</v>
       </c>
       <c r="B44" t="n">
-        <v>59.4036649837495</v>
+        <v>73.6304926610687</v>
       </c>
       <c r="C44" t="n">
-        <v>25.7186882032734</v>
+        <v>39.6159448269631</v>
       </c>
       <c r="D44" t="s">
         <v>27</v>
@@ -21478,16 +21478,16 @@
         <v>0.01</v>
       </c>
       <c r="G44" t="n">
-        <v>163.744970514928</v>
+        <v>191.28095587572</v>
       </c>
       <c r="H44" t="n">
-        <v>280.796457061763</v>
+        <v>311.297717449996</v>
       </c>
       <c r="I44" t="n">
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>4.71868820327338</v>
+        <v>18.6159448269631</v>
       </c>
       <c r="K44" t="s">
         <v>55</v>
@@ -21498,10 +21498,10 @@
         <v>45139</v>
       </c>
       <c r="B45" t="n">
-        <v>52.6724642425315</v>
+        <v>65.443307080516</v>
       </c>
       <c r="C45" t="n">
-        <v>17.3114279785071</v>
+        <v>29.9076163123029</v>
       </c>
       <c r="D45" t="s">
         <v>27</v>
@@ -21513,19 +21513,19 @@
         <v>0.01</v>
       </c>
       <c r="G45" t="n">
-        <v>162.180294214438</v>
+        <v>184.621329731235</v>
       </c>
       <c r="H45" t="n">
-        <v>258.620997621002</v>
+        <v>308.150676186692</v>
       </c>
       <c r="I45" t="n">
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.688572021492853</v>
+        <v>11.9076163123029</v>
       </c>
       <c r="K45" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46">
@@ -21533,10 +21533,10 @@
         <v>45170</v>
       </c>
       <c r="B46" t="n">
-        <v>45.2576245534111</v>
+        <v>55.3082339417801</v>
       </c>
       <c r="C46" t="n">
-        <v>12.9676450280826</v>
+        <v>21.5783397087253</v>
       </c>
       <c r="D46" t="s">
         <v>27</v>
@@ -21548,19 +21548,19 @@
         <v>0.01</v>
       </c>
       <c r="G46" t="n">
-        <v>128.619084164863</v>
+        <v>146.007231187422</v>
       </c>
       <c r="H46" t="n">
-        <v>242.605966094603</v>
+        <v>320.786629111939</v>
       </c>
       <c r="I46" t="n">
         <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>-7.0323549719174</v>
+        <v>1.57833970872531</v>
       </c>
       <c r="K46" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="47">
@@ -21568,10 +21568,10 @@
         <v>45200</v>
       </c>
       <c r="B47" t="n">
-        <v>40.3952300455098</v>
+        <v>50.1935356441596</v>
       </c>
       <c r="C47" t="n">
-        <v>6.81516348065544</v>
+        <v>15.4097423518313</v>
       </c>
       <c r="D47" t="s">
         <v>27</v>
@@ -21583,19 +21583,19 @@
         <v>0.01</v>
       </c>
       <c r="G47" t="n">
-        <v>120.808598084268</v>
+        <v>148.271097669097</v>
       </c>
       <c r="H47" t="n">
-        <v>247.032783380299</v>
+        <v>280.015830905594</v>
       </c>
       <c r="I47" t="n">
         <v>14</v>
       </c>
       <c r="J47" t="n">
-        <v>-7.18483651934456</v>
+        <v>1.40974235183127</v>
       </c>
       <c r="K47" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48">
@@ -21603,10 +21603,10 @@
         <v>45231</v>
       </c>
       <c r="B48" t="n">
-        <v>40.1467990412416</v>
+        <v>47.9235630336752</v>
       </c>
       <c r="C48" t="n">
-        <v>6.25618648594353</v>
+        <v>14.7481599037968</v>
       </c>
       <c r="D48" t="s">
         <v>27</v>
@@ -21618,19 +21618,19 @@
         <v>0.01</v>
       </c>
       <c r="G48" t="n">
-        <v>126.944540616743</v>
+        <v>133.199562977667</v>
       </c>
       <c r="H48" t="n">
-        <v>238.12297713733</v>
+        <v>264.866615177048</v>
       </c>
       <c r="I48" t="n">
         <v>9</v>
       </c>
       <c r="J48" t="n">
-        <v>-2.74381351405647</v>
+        <v>5.74815990379675</v>
       </c>
       <c r="K48" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49">
@@ -21638,10 +21638,10 @@
         <v>45261</v>
       </c>
       <c r="B49" t="n">
-        <v>41.0951333152301</v>
+        <v>48.2527378626844</v>
       </c>
       <c r="C49" t="n">
-        <v>6.58376370468039</v>
+        <v>13.754479345646</v>
       </c>
       <c r="D49" t="s">
         <v>27</v>
@@ -21653,19 +21653,19 @@
         <v>0.01</v>
       </c>
       <c r="G49" t="n">
-        <v>123.754505573807</v>
+        <v>135.720885941179</v>
       </c>
       <c r="H49" t="n">
-        <v>254.202117527919</v>
+        <v>255.871486806572</v>
       </c>
       <c r="I49" t="n">
         <v>8</v>
       </c>
       <c r="J49" t="n">
-        <v>-1.41623629531961</v>
+        <v>5.75447934564596</v>
       </c>
       <c r="K49" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="50">
@@ -21673,10 +21673,10 @@
         <v>45292</v>
       </c>
       <c r="B50" t="n">
-        <v>78.6639576462681</v>
+        <v>87.4195413023612</v>
       </c>
       <c r="C50" t="n">
-        <v>36.3265351484778</v>
+        <v>45.9994158647448</v>
       </c>
       <c r="D50" t="s">
         <v>27</v>
@@ -21688,16 +21688,16 @@
         <v>0.01</v>
       </c>
       <c r="G50" t="n">
-        <v>211.110909858961</v>
+        <v>246.262989141759</v>
       </c>
       <c r="H50" t="n">
-        <v>356.967801791339</v>
+        <v>409.86923338045</v>
       </c>
       <c r="I50" t="n">
         <v>35</v>
       </c>
       <c r="J50" t="n">
-        <v>1.32653514847777</v>
+        <v>10.9994158647448</v>
       </c>
       <c r="K50" t="s">
         <v>55</v>
@@ -21708,10 +21708,10 @@
         <v>45323</v>
       </c>
       <c r="B51" t="n">
-        <v>71.1678047658435</v>
+        <v>84.0870620147396</v>
       </c>
       <c r="C51" t="n">
-        <v>30.3229253413982</v>
+        <v>45.2022022683935</v>
       </c>
       <c r="D51" t="s">
         <v>27</v>
@@ -21723,16 +21723,16 @@
         <v>0.01</v>
       </c>
       <c r="G51" t="n">
-        <v>197.594365050086</v>
+        <v>226.016991259769</v>
       </c>
       <c r="H51" t="n">
-        <v>368.247302249783</v>
+        <v>432.262908761606</v>
       </c>
       <c r="I51" t="n">
         <v>11</v>
       </c>
       <c r="J51" t="n">
-        <v>19.3229253413982</v>
+        <v>34.2022022683935</v>
       </c>
       <c r="K51" t="s">
         <v>55</v>
@@ -21743,10 +21743,10 @@
         <v>45352</v>
       </c>
       <c r="B52" t="n">
-        <v>67.4551634892655</v>
+        <v>77.8642989203978</v>
       </c>
       <c r="C52" t="n">
-        <v>26.5753106720603</v>
+        <v>36.1780719317757</v>
       </c>
       <c r="D52" t="s">
         <v>27</v>
@@ -21758,16 +21758,16 @@
         <v>0.01</v>
       </c>
       <c r="G52" t="n">
-        <v>198.042428125933</v>
+        <v>202.423180091131</v>
       </c>
       <c r="H52" t="n">
-        <v>355.491839776936</v>
+        <v>376.384038170248</v>
       </c>
       <c r="I52" t="n">
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>5.57531067206029</v>
+        <v>15.1780719317757</v>
       </c>
       <c r="K52" t="s">
         <v>55</v>
@@ -21778,10 +21778,10 @@
         <v>45383</v>
       </c>
       <c r="B53" t="n">
-        <v>53.617586637107</v>
+        <v>64.8031023639777</v>
       </c>
       <c r="C53" t="n">
-        <v>15.096106708282</v>
+        <v>23.4088086474296</v>
       </c>
       <c r="D53" t="s">
         <v>27</v>
@@ -21793,16 +21793,16 @@
         <v>0.01</v>
       </c>
       <c r="G53" t="n">
-        <v>150.611731845786</v>
+        <v>186.458070516439</v>
       </c>
       <c r="H53" t="n">
-        <v>316.434373326492</v>
+        <v>330.427654711707</v>
       </c>
       <c r="I53" t="n">
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>-10.903893291718</v>
+        <v>-2.59119135257039</v>
       </c>
       <c r="K53" t="s">
         <v>54</v>
@@ -21813,10 +21813,10 @@
         <v>45413</v>
       </c>
       <c r="B54" t="n">
-        <v>69.523434502279</v>
+        <v>83.5548475778439</v>
       </c>
       <c r="C54" t="n">
-        <v>24.4298392168261</v>
+        <v>42.420778311675</v>
       </c>
       <c r="D54" t="s">
         <v>27</v>
@@ -21828,19 +21828,19 @@
         <v>0.01</v>
       </c>
       <c r="G54" t="n">
-        <v>180.449930496253</v>
+        <v>239.894689509155</v>
       </c>
       <c r="H54" t="n">
-        <v>391.592284867105</v>
+        <v>421.454263338846</v>
       </c>
       <c r="I54" t="n">
         <v>29</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.57016078317388</v>
+        <v>13.420778311675</v>
       </c>
       <c r="K54" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55">
@@ -21848,10 +21848,10 @@
         <v>45444</v>
       </c>
       <c r="B55" t="n">
-        <v>76.4492736292564</v>
+        <v>90.2988959379091</v>
       </c>
       <c r="C55" t="n">
-        <v>28.6630056482252</v>
+        <v>47.3124524838988</v>
       </c>
       <c r="D55" t="s">
         <v>27</v>
@@ -21863,16 +21863,16 @@
         <v>0.01</v>
       </c>
       <c r="G55" t="n">
-        <v>201.838568119755</v>
+        <v>252.794707888147</v>
       </c>
       <c r="H55" t="n">
-        <v>413.226937108552</v>
+        <v>380.281067468915</v>
       </c>
       <c r="I55" t="n">
         <v>22</v>
       </c>
       <c r="J55" t="n">
-        <v>6.66300564822524</v>
+        <v>25.3124524838988</v>
       </c>
       <c r="K55" t="s">
         <v>55</v>
@@ -21883,10 +21883,10 @@
         <v>45474</v>
       </c>
       <c r="B56" t="n">
-        <v>61.8906050141308</v>
+        <v>74.8404474841727</v>
       </c>
       <c r="C56" t="n">
-        <v>16.4978547298059</v>
+        <v>33.8149110040712</v>
       </c>
       <c r="D56" t="s">
         <v>27</v>
@@ -21898,16 +21898,16 @@
         <v>0.01</v>
       </c>
       <c r="G56" t="n">
-        <v>177.063204564482</v>
+        <v>232.872027704664</v>
       </c>
       <c r="H56" t="n">
-        <v>355.855268021243</v>
+        <v>375.298592136702</v>
       </c>
       <c r="I56" t="n">
         <v>40</v>
       </c>
       <c r="J56" t="n">
-        <v>-23.5021452701941</v>
+        <v>-6.18508899592877</v>
       </c>
       <c r="K56" t="s">
         <v>54</v>
@@ -21918,10 +21918,10 @@
         <v>45505</v>
       </c>
       <c r="B57" t="n">
-        <v>54.697361679784</v>
+        <v>65.1233809360276</v>
       </c>
       <c r="C57" t="n">
-        <v>8.59925724032679</v>
+        <v>22.2145912107367</v>
       </c>
       <c r="D57" t="s">
         <v>27</v>
@@ -21933,16 +21933,16 @@
         <v>0.01</v>
       </c>
       <c r="G57" t="n">
-        <v>164.752633229962</v>
+        <v>195.21024107852</v>
       </c>
       <c r="H57" t="n">
-        <v>339.34871721312</v>
+        <v>314.764821026753</v>
       </c>
       <c r="I57" t="n">
         <v>31</v>
       </c>
       <c r="J57" t="n">
-        <v>-22.4007427596732</v>
+        <v>-8.78540878926334</v>
       </c>
       <c r="K57" t="s">
         <v>54</v>
@@ -21953,10 +21953,10 @@
         <v>45536</v>
       </c>
       <c r="B58" t="n">
-        <v>47.6564898788086</v>
+        <v>55.8528337505865</v>
       </c>
       <c r="C58" t="n">
-        <v>4.79770959361959</v>
+        <v>15.2805746261208</v>
       </c>
       <c r="D58" t="s">
         <v>27</v>
@@ -21968,19 +21968,19 @@
         <v>0.01</v>
       </c>
       <c r="G58" t="n">
-        <v>149.336899575571</v>
+        <v>173.705892155305</v>
       </c>
       <c r="H58" t="n">
-        <v>339.397990084769</v>
+        <v>332.22977800052</v>
       </c>
       <c r="I58" t="n">
         <v>10</v>
       </c>
       <c r="J58" t="n">
-        <v>-5.20229040638041</v>
+        <v>5.28057462612075</v>
       </c>
       <c r="K58" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59">
@@ -21988,10 +21988,10 @@
         <v>45566</v>
       </c>
       <c r="B59" t="n">
-        <v>41.5478396009483</v>
+        <v>48.2297257727133</v>
       </c>
       <c r="C59" t="n">
-        <v>2.98272914883452</v>
+        <v>12.2495738278548</v>
       </c>
       <c r="D59" t="s">
         <v>27</v>
@@ -22003,16 +22003,16 @@
         <v>0.01</v>
       </c>
       <c r="G59" t="n">
-        <v>131.901924212827</v>
+        <v>145.885576304892</v>
       </c>
       <c r="H59" t="n">
-        <v>330.722957890609</v>
+        <v>280.710709169999</v>
       </c>
       <c r="I59" t="n">
         <v>14</v>
       </c>
       <c r="J59" t="n">
-        <v>-11.0172708511655</v>
+        <v>-1.75042617214515</v>
       </c>
       <c r="K59" t="s">
         <v>54</v>
@@ -22023,10 +22023,10 @@
         <v>45597</v>
       </c>
       <c r="B60" t="n">
-        <v>42.8466138434441</v>
+        <v>49.1619713481242</v>
       </c>
       <c r="C60" t="n">
-        <v>2.82682024598992</v>
+        <v>13.3080416003162</v>
       </c>
       <c r="D60" t="s">
         <v>27</v>
@@ -22038,16 +22038,16 @@
         <v>0.01</v>
       </c>
       <c r="G60" t="n">
-        <v>142.062882180099</v>
+        <v>150.663321932917</v>
       </c>
       <c r="H60" t="n">
-        <v>350.884757869725</v>
+        <v>300.461753769548</v>
       </c>
       <c r="I60" t="n">
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>-14.1731797540101</v>
+        <v>-3.69195839968384</v>
       </c>
       <c r="K60" t="s">
         <v>54</v>
@@ -22058,10 +22058,10 @@
         <v>45627</v>
       </c>
       <c r="B61" t="n">
-        <v>43.67449552814</v>
+        <v>48.3670176497679</v>
       </c>
       <c r="C61" t="n">
-        <v>2.17882853148483</v>
+        <v>10.5681039168878</v>
       </c>
       <c r="D61" t="s">
         <v>27</v>
@@ -22073,16 +22073,16 @@
         <v>0.01</v>
       </c>
       <c r="G61" t="n">
-        <v>145.908550518896</v>
+        <v>142.895031172547</v>
       </c>
       <c r="H61" t="n">
-        <v>296.513477970647</v>
+        <v>333.77459028471</v>
       </c>
       <c r="I61" t="n">
         <v>11</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.82117146851517</v>
+        <v>-0.431896083112179</v>
       </c>
       <c r="K61" t="s">
         <v>54</v>
@@ -22093,10 +22093,10 @@
         <v>45658</v>
       </c>
       <c r="B62" t="n">
-        <v>75.9222552057361</v>
+        <v>88.1698461629027</v>
       </c>
       <c r="C62" t="n">
-        <v>20.0281707629913</v>
+        <v>42.1353793123589</v>
       </c>
       <c r="D62" t="s">
         <v>27</v>
@@ -22108,19 +22108,19 @@
         <v>0.01</v>
       </c>
       <c r="G62" t="n">
-        <v>230.191483404548</v>
+        <v>232.147615940301</v>
       </c>
       <c r="H62" t="n">
-        <v>429.814195812693</v>
+        <v>468.900002905697</v>
       </c>
       <c r="I62" t="n">
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-1.97182923700871</v>
+        <v>20.1353793123589</v>
       </c>
       <c r="K62" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="63">
@@ -22128,10 +22128,10 @@
         <v>45689</v>
       </c>
       <c r="B63" t="n">
-        <v>70.448310898745</v>
+        <v>82.7952550555744</v>
       </c>
       <c r="C63" t="n">
-        <v>19.56710370677</v>
+        <v>33.9061909082197</v>
       </c>
       <c r="D63" t="s">
         <v>27</v>
@@ -22143,16 +22143,16 @@
         <v>0.01</v>
       </c>
       <c r="G63" t="n">
-        <v>218.676332200768</v>
+        <v>224.818260950978</v>
       </c>
       <c r="H63" t="n">
-        <v>401.957436468084</v>
+        <v>431.012038000452</v>
       </c>
       <c r="I63" t="n">
         <v>34</v>
       </c>
       <c r="J63" t="n">
-        <v>-14.43289629323</v>
+        <v>-0.0938090917803365</v>
       </c>
       <c r="K63" t="s">
         <v>54</v>
@@ -22163,10 +22163,10 @@
         <v>45717</v>
       </c>
       <c r="B64" t="n">
-        <v>66.6479284756743</v>
+        <v>78.8156177508014</v>
       </c>
       <c r="C64" t="n">
-        <v>15.3165701504695</v>
+        <v>27.6356006678369</v>
       </c>
       <c r="D64" t="s">
         <v>27</v>
@@ -22178,16 +22178,16 @@
         <v>0.01</v>
       </c>
       <c r="G64" t="n">
-        <v>204.225233354015</v>
+        <v>207.357191821892</v>
       </c>
       <c r="H64" t="n">
-        <v>415.753068163134</v>
+        <v>401.420867372961</v>
       </c>
       <c r="I64" t="n">
         <v>31</v>
       </c>
       <c r="J64" t="n">
-        <v>-15.6834298495305</v>
+        <v>-3.36439933216308</v>
       </c>
       <c r="K64" t="s">
         <v>54</v>
@@ -22198,10 +22198,10 @@
         <v>45748</v>
       </c>
       <c r="B65" t="n">
-        <v>56.2652949477619</v>
+        <v>66.5312910664891</v>
       </c>
       <c r="C65" t="n">
-        <v>6.70035246744374</v>
+        <v>16.8399178448519</v>
       </c>
       <c r="D65" t="s">
         <v>27</v>
@@ -22213,16 +22213,16 @@
         <v>0.01</v>
       </c>
       <c r="G65" t="n">
-        <v>179.608606321851</v>
+        <v>198.523032176471</v>
       </c>
       <c r="H65" t="n">
-        <v>343.687580501526</v>
+        <v>385.258621090267</v>
       </c>
       <c r="I65" t="n">
         <v>29</v>
       </c>
       <c r="J65" t="n">
-        <v>-22.2996475325563</v>
+        <v>-12.1600821551481</v>
       </c>
       <c r="K65" t="s">
         <v>54</v>
@@ -22233,10 +22233,10 @@
         <v>45778</v>
       </c>
       <c r="B66" t="n">
-        <v>72.8370334656308</v>
+        <v>83.0408522591917</v>
       </c>
       <c r="C66" t="n">
-        <v>16.0565271269733</v>
+        <v>29.9281822507795</v>
       </c>
       <c r="D66" t="s">
         <v>27</v>
@@ -22248,19 +22248,19 @@
         <v>0.01</v>
       </c>
       <c r="G66" t="n">
-        <v>228.350143726228</v>
+        <v>244.467231562419</v>
       </c>
       <c r="H66" t="n">
-        <v>428.692430129174</v>
+        <v>397.911152963732</v>
       </c>
       <c r="I66" t="n">
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>-5.94347287302673</v>
+        <v>7.92818225077952</v>
       </c>
       <c r="K66" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67">
@@ -22268,10 +22268,10 @@
         <v>45809</v>
       </c>
       <c r="B67" t="n">
-        <v>75.586090407653</v>
+        <v>91.8347872156971</v>
       </c>
       <c r="C67" t="n">
-        <v>21.0914009015687</v>
+        <v>37.103214618812</v>
       </c>
       <c r="D67" t="s">
         <v>27</v>
@@ -22283,19 +22283,19 @@
         <v>0.01</v>
       </c>
       <c r="G67" t="n">
-        <v>208.316793423186</v>
+        <v>264.224794508955</v>
       </c>
       <c r="H67" t="n">
-        <v>472.857859194063</v>
+        <v>489.449839733146</v>
       </c>
       <c r="I67" t="n">
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-3.90859909843133</v>
+        <v>12.103214618812</v>
       </c>
       <c r="K67" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="68">
@@ -22303,10 +22303,10 @@
         <v>45839</v>
       </c>
       <c r="B68" t="n">
-        <v>60.9310360560885</v>
+        <v>75.933228401731</v>
       </c>
       <c r="C68" t="n">
-        <v>11.7070850756089</v>
+        <v>18.8327641258115</v>
       </c>
       <c r="D68" t="s">
         <v>27</v>
@@ -22318,16 +22318,16 @@
         <v>0.01</v>
       </c>
       <c r="G68" t="n">
-        <v>192.005323348012</v>
+        <v>235.217416353643</v>
       </c>
       <c r="H68" t="n">
-        <v>361.199301710263</v>
+        <v>433.477438527327</v>
       </c>
       <c r="I68" t="n">
         <v>30</v>
       </c>
       <c r="J68" t="n">
-        <v>-18.2929149243911</v>
+        <v>-11.1672358741885</v>
       </c>
       <c r="K68" t="s">
         <v>54</v>
@@ -22338,10 +22338,10 @@
         <v>45870</v>
       </c>
       <c r="B69" t="n">
-        <v>55.2722830396491</v>
+        <v>68.1781274895813</v>
       </c>
       <c r="C69" t="n">
-        <v>7.83904571339251</v>
+        <v>13.1478429715563</v>
       </c>
       <c r="D69" t="s">
         <v>27</v>
@@ -22353,16 +22353,16 @@
         <v>0.01</v>
       </c>
       <c r="G69" t="n">
-        <v>162.646280313171</v>
+        <v>221.471666796391</v>
       </c>
       <c r="H69" t="n">
-        <v>403.975073937525</v>
+        <v>401.716586731334</v>
       </c>
       <c r="I69" t="n">
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>-18.1609542866075</v>
+        <v>-12.8521570284437</v>
       </c>
       <c r="K69" t="s">
         <v>54</v>
@@ -22373,10 +22373,10 @@
         <v>45901</v>
       </c>
       <c r="B70" t="n">
-        <v>49.3140989577107</v>
+        <v>59.1208958325532</v>
       </c>
       <c r="C70" t="n">
-        <v>3.35029012088559</v>
+        <v>9.31775696672869</v>
       </c>
       <c r="D70" t="s">
         <v>27</v>
@@ -22388,16 +22388,16 @@
         <v>0.01</v>
       </c>
       <c r="G70" t="n">
-        <v>148.200536634102</v>
+        <v>184.907927144587</v>
       </c>
       <c r="H70" t="n">
-        <v>397.865316893413</v>
+        <v>332.615974887436</v>
       </c>
       <c r="I70" t="n">
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-18.6497098791144</v>
+        <v>-12.6822430332713</v>
       </c>
       <c r="K70" t="s">
         <v>54</v>
@@ -22408,10 +22408,10 @@
         <v>45931</v>
       </c>
       <c r="B71" t="n">
-        <v>44.7091288068846</v>
+        <v>53.9916485331323</v>
       </c>
       <c r="C71" t="n">
-        <v>1.62273529458453</v>
+        <v>3.64308201628634</v>
       </c>
       <c r="D71" t="s">
         <v>27</v>
@@ -22423,16 +22423,16 @@
         <v>0.01</v>
       </c>
       <c r="G71" t="n">
-        <v>132.058574268503</v>
+        <v>180.451558141936</v>
       </c>
       <c r="H71" t="n">
-        <v>350.929008126579</v>
+        <v>339.006895739599</v>
       </c>
       <c r="I71" t="n">
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-19.3772647054155</v>
+        <v>-17.3569179837137</v>
       </c>
       <c r="K71" t="s">
         <v>54</v>
@@ -22443,10 +22443,10 @@
         <v>45962</v>
       </c>
       <c r="B72" t="n">
-        <v>43.9564938709598</v>
+        <v>54.3701620957664</v>
       </c>
       <c r="C72" t="n">
-        <v>0.919654633765553</v>
+        <v>2.85526321100815</v>
       </c>
       <c r="D72" t="s">
         <v>27</v>
@@ -22458,16 +22458,16 @@
         <v>0.01</v>
       </c>
       <c r="G72" t="n">
-        <v>136.044247159077</v>
+        <v>160.558037481661</v>
       </c>
       <c r="H72" t="n">
-        <v>324.45855162525</v>
+        <v>356.469811046365</v>
       </c>
       <c r="I72" t="n">
         <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>-27.0803453662344</v>
+        <v>-25.1447367889918</v>
       </c>
       <c r="K72" t="s">
         <v>54</v>
@@ -22478,10 +22478,10 @@
         <v>45992</v>
       </c>
       <c r="B73" t="n">
-        <v>45.6480234505281</v>
+        <v>54.1486145968342</v>
       </c>
       <c r="C73" t="n">
-        <v>0.545283696837193</v>
+        <v>4.55372635507665</v>
       </c>
       <c r="D73" t="s">
         <v>27</v>
@@ -22493,16 +22493,16 @@
         <v>0.01</v>
       </c>
       <c r="G73" t="n">
-        <v>134.047000889089</v>
+        <v>165.952907274777</v>
       </c>
       <c r="H73" t="n">
-        <v>345.360567212058</v>
+        <v>403.623406058087</v>
       </c>
       <c r="I73" t="n">
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-20.4547163031628</v>
+        <v>-16.4462736449234</v>
       </c>
       <c r="K73" t="s">
         <v>54</v>
@@ -54342,31 +54342,31 @@
         <v>43831</v>
       </c>
       <c r="B2" t="n">
-        <v>175.515559712954</v>
+        <v>201.972416418421</v>
       </c>
       <c r="C2" t="n">
-        <v>178.142423174524</v>
+        <v>201.931204627775</v>
       </c>
       <c r="D2" t="s">
         <v>40</v>
       </c>
       <c r="E2" t="n">
-        <v>122.887625190924</v>
+        <v>199.693277938551</v>
       </c>
       <c r="F2" t="n">
-        <v>89.7689416006188</v>
+        <v>198.96120224631</v>
       </c>
       <c r="G2" t="n">
-        <v>220.853778771476</v>
+        <v>204.279660488705</v>
       </c>
       <c r="H2" t="n">
-        <v>266.097541501315</v>
+        <v>205.252239967691</v>
       </c>
       <c r="I2" t="n">
         <v>164</v>
       </c>
       <c r="J2" t="n">
-        <v>14.1424231745235</v>
+        <v>37.9312046277751</v>
       </c>
       <c r="K2" t="s">
         <v>55</v>
@@ -54377,31 +54377,31 @@
         <v>43862</v>
       </c>
       <c r="B3" t="n">
-        <v>189.662988792238</v>
+        <v>213.56746958666</v>
       </c>
       <c r="C3" t="n">
-        <v>184.940512000127</v>
+        <v>213.576625790401</v>
       </c>
       <c r="D3" t="s">
         <v>40</v>
       </c>
       <c r="E3" t="n">
-        <v>112.059765335503</v>
+        <v>211.193893545793</v>
       </c>
       <c r="F3" t="n">
-        <v>81.3461729403192</v>
+        <v>210.441013214554</v>
       </c>
       <c r="G3" t="n">
-        <v>263.332672699114</v>
+        <v>215.909756330184</v>
       </c>
       <c r="H3" t="n">
-        <v>356.943044852696</v>
+        <v>216.909605730101</v>
       </c>
       <c r="I3" t="n">
         <v>138</v>
       </c>
       <c r="J3" t="n">
-        <v>46.9405120001269</v>
+        <v>75.5766257904012</v>
       </c>
       <c r="K3" t="s">
         <v>55</v>
@@ -54412,31 +54412,31 @@
         <v>43891</v>
       </c>
       <c r="B4" t="n">
-        <v>232.98205647765</v>
+        <v>241.158156499152</v>
       </c>
       <c r="C4" t="n">
-        <v>222.361286887249</v>
+        <v>241.077288583851</v>
       </c>
       <c r="D4" t="s">
         <v>40</v>
       </c>
       <c r="E4" t="n">
-        <v>131.502199528069</v>
+        <v>238.631466495058</v>
       </c>
       <c r="F4" t="n">
-        <v>91.418714213929</v>
+        <v>237.831130961758</v>
       </c>
       <c r="G4" t="n">
-        <v>336.148484013974</v>
+        <v>243.835734448246</v>
       </c>
       <c r="H4" t="n">
-        <v>463.80316009543</v>
+        <v>244.70472443093</v>
       </c>
       <c r="I4" t="n">
         <v>108</v>
       </c>
       <c r="J4" t="n">
-        <v>114.361286887249</v>
+        <v>133.077288583851</v>
       </c>
       <c r="K4" t="s">
         <v>55</v>
@@ -54447,31 +54447,31 @@
         <v>43922</v>
       </c>
       <c r="B5" t="n">
-        <v>195.231928826765</v>
+        <v>184.607744138848</v>
       </c>
       <c r="C5" t="n">
-        <v>182.527717476957</v>
+        <v>184.61643366616</v>
       </c>
       <c r="D5" t="s">
         <v>40</v>
       </c>
       <c r="E5" t="n">
-        <v>94.7143185780729</v>
+        <v>182.40159809214</v>
       </c>
       <c r="F5" t="n">
-        <v>54.3965289882304</v>
+        <v>181.701965376239</v>
       </c>
       <c r="G5" t="n">
-        <v>311.974423862925</v>
+        <v>186.955113546478</v>
       </c>
       <c r="H5" t="n">
-        <v>421.923526444322</v>
+        <v>187.716122254515</v>
       </c>
       <c r="I5" t="n">
         <v>60</v>
       </c>
       <c r="J5" t="n">
-        <v>122.527717476957</v>
+        <v>124.61643366616</v>
       </c>
       <c r="K5" t="s">
         <v>55</v>
@@ -54482,31 +54482,31 @@
         <v>43952</v>
       </c>
       <c r="B6" t="n">
-        <v>228.108915204268</v>
+        <v>179.838390680687</v>
       </c>
       <c r="C6" t="n">
-        <v>213.923190824817</v>
+        <v>179.848642381572</v>
       </c>
       <c r="D6" t="s">
         <v>40</v>
       </c>
       <c r="E6" t="n">
-        <v>109.947495849864</v>
+        <v>177.661978233528</v>
       </c>
       <c r="F6" t="n">
-        <v>66.0689578714225</v>
+        <v>176.971503950517</v>
       </c>
       <c r="G6" t="n">
-        <v>363.697619891238</v>
+        <v>181.989449287442</v>
       </c>
       <c r="H6" t="n">
-        <v>490.9986613995</v>
+        <v>182.907499238642</v>
       </c>
       <c r="I6" t="n">
         <v>85</v>
       </c>
       <c r="J6" t="n">
-        <v>128.923190824817</v>
+        <v>94.8486423815719</v>
       </c>
       <c r="K6" t="s">
         <v>55</v>
@@ -54517,31 +54517,31 @@
         <v>43983</v>
       </c>
       <c r="B7" t="n">
-        <v>244.972765822556</v>
+        <v>197.821943514916</v>
       </c>
       <c r="C7" t="n">
-        <v>228.534957657236</v>
+        <v>197.788428070281</v>
       </c>
       <c r="D7" t="s">
         <v>40</v>
       </c>
       <c r="E7" t="n">
-        <v>113.786269958716</v>
+        <v>195.637418479585</v>
       </c>
       <c r="F7" t="n">
-        <v>68.4649957347182</v>
+        <v>194.849162970965</v>
       </c>
       <c r="G7" t="n">
-        <v>394.581407364344</v>
+        <v>200.095209821785</v>
       </c>
       <c r="H7" t="n">
-        <v>530.30122487218</v>
+        <v>200.999680262975</v>
       </c>
       <c r="I7" t="n">
         <v>56</v>
       </c>
       <c r="J7" t="n">
-        <v>172.534957657236</v>
+        <v>141.788428070281</v>
       </c>
       <c r="K7" t="s">
         <v>55</v>
@@ -54552,31 +54552,31 @@
         <v>44013</v>
       </c>
       <c r="B8" t="n">
-        <v>262.434307946797</v>
+        <v>211.903372433254</v>
       </c>
       <c r="C8" t="n">
-        <v>245.701522658317</v>
+        <v>211.830021095461</v>
       </c>
       <c r="D8" t="s">
         <v>40</v>
       </c>
       <c r="E8" t="n">
-        <v>118.094373658773</v>
+        <v>209.579058802734</v>
       </c>
       <c r="F8" t="n">
-        <v>67.3940608624889</v>
+        <v>208.829064913406</v>
       </c>
       <c r="G8" t="n">
-        <v>429.29088787333</v>
+        <v>214.276957460236</v>
       </c>
       <c r="H8" t="n">
-        <v>571.47304566873</v>
+        <v>215.273023423069</v>
       </c>
       <c r="I8" t="n">
         <v>76</v>
       </c>
       <c r="J8" t="n">
-        <v>169.701522658317</v>
+        <v>135.830021095461</v>
       </c>
       <c r="K8" t="s">
         <v>55</v>
@@ -54587,31 +54587,31 @@
         <v>44044</v>
       </c>
       <c r="B9" t="n">
-        <v>242.219135475954</v>
+        <v>207.137758014576</v>
       </c>
       <c r="C9" t="n">
-        <v>221.507410435362</v>
+        <v>207.179409522248</v>
       </c>
       <c r="D9" t="s">
         <v>40</v>
       </c>
       <c r="E9" t="n">
-        <v>97.418376962681</v>
+        <v>204.832734159975</v>
       </c>
       <c r="F9" t="n">
-        <v>54.0179470749322</v>
+        <v>204.091289094212</v>
       </c>
       <c r="G9" t="n">
-        <v>410.337831902568</v>
+        <v>209.47742816068</v>
       </c>
       <c r="H9" t="n">
-        <v>539.098923211644</v>
+        <v>210.462288654257</v>
       </c>
       <c r="I9" t="n">
         <v>79</v>
       </c>
       <c r="J9" t="n">
-        <v>142.507410435362</v>
+        <v>128.179409522248</v>
       </c>
       <c r="K9" t="s">
         <v>55</v>
@@ -54622,31 +54622,31 @@
         <v>44075</v>
       </c>
       <c r="B10" t="n">
-        <v>223.253469797281</v>
+        <v>197.641464075488</v>
       </c>
       <c r="C10" t="n">
-        <v>202.420828856058</v>
+        <v>197.640987964386</v>
       </c>
       <c r="D10" t="s">
         <v>40</v>
       </c>
       <c r="E10" t="n">
-        <v>81.6363561038616</v>
+        <v>195.412865368085</v>
       </c>
       <c r="F10" t="n">
-        <v>40.4663422622041</v>
+        <v>194.625062826889</v>
       </c>
       <c r="G10" t="n">
-        <v>389.538106682501</v>
+        <v>199.885631170536</v>
       </c>
       <c r="H10" t="n">
-        <v>521.09943440238</v>
+        <v>200.772069668404</v>
       </c>
       <c r="I10" t="n">
         <v>60</v>
       </c>
       <c r="J10" t="n">
-        <v>142.420828856058</v>
+        <v>137.640987964386</v>
       </c>
       <c r="K10" t="s">
         <v>55</v>
@@ -54657,31 +54657,31 @@
         <v>44105</v>
       </c>
       <c r="B11" t="n">
-        <v>200.265092054064</v>
+        <v>174.452435457787</v>
       </c>
       <c r="C11" t="n">
-        <v>178.578375000745</v>
+        <v>174.469378031359</v>
       </c>
       <c r="D11" t="s">
         <v>40</v>
       </c>
       <c r="E11" t="n">
-        <v>62.9137204685567</v>
+        <v>172.375975663645</v>
       </c>
       <c r="F11" t="n">
-        <v>27.4128873006767</v>
+        <v>171.636113565603</v>
       </c>
       <c r="G11" t="n">
-        <v>361.460836682649</v>
+        <v>176.578371532811</v>
       </c>
       <c r="H11" t="n">
-        <v>507.987357722325</v>
+        <v>177.482687642784</v>
       </c>
       <c r="I11" t="n">
         <v>94</v>
       </c>
       <c r="J11" t="n">
-        <v>84.5783750007447</v>
+        <v>80.4693780313593</v>
       </c>
       <c r="K11" t="s">
         <v>55</v>
@@ -54692,31 +54692,31 @@
         <v>44136</v>
       </c>
       <c r="B12" t="n">
-        <v>167.989899361901</v>
+        <v>155.169607925836</v>
       </c>
       <c r="C12" t="n">
-        <v>144.458430406336</v>
+        <v>155.172042055323</v>
       </c>
       <c r="D12" t="s">
         <v>40</v>
       </c>
       <c r="E12" t="n">
-        <v>42.1719763161769</v>
+        <v>153.142051106473</v>
       </c>
       <c r="F12" t="n">
-        <v>11.3467478002574</v>
+        <v>152.501040967566</v>
       </c>
       <c r="G12" t="n">
-        <v>322.540556964531</v>
+        <v>157.161675964861</v>
       </c>
       <c r="H12" t="n">
-        <v>455.709525304724</v>
+        <v>158.014890217698</v>
       </c>
       <c r="I12" t="n">
         <v>48</v>
       </c>
       <c r="J12" t="n">
-        <v>96.4584304063356</v>
+        <v>107.172042055323</v>
       </c>
       <c r="K12" t="s">
         <v>55</v>
@@ -54727,31 +54727,31 @@
         <v>44166</v>
       </c>
       <c r="B13" t="n">
-        <v>157.510085383233</v>
+        <v>134.897455437412</v>
       </c>
       <c r="C13" t="n">
-        <v>133.913083032992</v>
+        <v>134.909974467866</v>
       </c>
       <c r="D13" t="s">
         <v>40</v>
       </c>
       <c r="E13" t="n">
-        <v>34.075686490048</v>
+        <v>133.01699828421</v>
       </c>
       <c r="F13" t="n">
-        <v>8.23017331873823</v>
+        <v>132.419635722026</v>
       </c>
       <c r="G13" t="n">
-        <v>307.230529407837</v>
+        <v>136.76497707084</v>
       </c>
       <c r="H13" t="n">
-        <v>439.326474098501</v>
+        <v>137.560979758207</v>
       </c>
       <c r="I13" t="n">
         <v>48</v>
       </c>
       <c r="J13" t="n">
-        <v>85.9130830329923</v>
+        <v>86.9099744678656</v>
       </c>
       <c r="K13" t="s">
         <v>55</v>
@@ -54762,31 +54762,31 @@
         <v>44197</v>
       </c>
       <c r="B14" t="n">
-        <v>199.554171110678</v>
+        <v>202.007925631586</v>
       </c>
       <c r="C14" t="n">
-        <v>171.136110040986</v>
+        <v>202.010592158625</v>
       </c>
       <c r="D14" t="s">
         <v>40</v>
       </c>
       <c r="E14" t="n">
-        <v>48.2279310770613</v>
+        <v>199.69345860695</v>
       </c>
       <c r="F14" t="n">
-        <v>12.3255009517126</v>
+        <v>198.961382583239</v>
       </c>
       <c r="G14" t="n">
-        <v>384.212355539582</v>
+        <v>204.456626225679</v>
       </c>
       <c r="H14" t="n">
-        <v>545.546323297871</v>
+        <v>205.929314464754</v>
       </c>
       <c r="I14" t="n">
         <v>62</v>
       </c>
       <c r="J14" t="n">
-        <v>109.136110040986</v>
+        <v>140.010592158625</v>
       </c>
       <c r="K14" t="s">
         <v>55</v>
@@ -54797,31 +54797,31 @@
         <v>44228</v>
       </c>
       <c r="B15" t="n">
-        <v>215.075172013307</v>
+        <v>213.531263941109</v>
       </c>
       <c r="C15" t="n">
-        <v>183.048383233649</v>
+        <v>213.495375906918</v>
       </c>
       <c r="D15" t="s">
         <v>40</v>
       </c>
       <c r="E15" t="n">
-        <v>48.5064787089231</v>
+        <v>211.194084587393</v>
       </c>
       <c r="F15" t="n">
-        <v>12.2177945169785</v>
+        <v>210.44120391533</v>
       </c>
       <c r="G15" t="n">
-        <v>421.017511224212</v>
+        <v>215.891741670555</v>
       </c>
       <c r="H15" t="n">
-        <v>590.480783412777</v>
+        <v>216.909799339599</v>
       </c>
       <c r="I15" t="n">
         <v>67</v>
       </c>
       <c r="J15" t="n">
-        <v>116.048383233649</v>
+        <v>146.495375906918</v>
       </c>
       <c r="K15" t="s">
         <v>55</v>
@@ -54832,31 +54832,31 @@
         <v>44256</v>
       </c>
       <c r="B16" t="n">
-        <v>257.972146917551</v>
+        <v>241.099156307571</v>
       </c>
       <c r="C16" t="n">
-        <v>224.55768531555</v>
+        <v>241.033197949569</v>
       </c>
       <c r="D16" t="s">
         <v>40</v>
       </c>
       <c r="E16" t="n">
-        <v>63.380093552217</v>
+        <v>238.631682281271</v>
       </c>
       <c r="F16" t="n">
-        <v>20.5715474333738</v>
+        <v>237.831346385809</v>
       </c>
       <c r="G16" t="n">
-        <v>495.017847539459</v>
+        <v>243.623548718802</v>
       </c>
       <c r="H16" t="n">
-        <v>692.319957275139</v>
+        <v>244.621455024584</v>
       </c>
       <c r="I16" t="n">
         <v>82</v>
       </c>
       <c r="J16" t="n">
-        <v>142.55768531555</v>
+        <v>159.033197949569</v>
       </c>
       <c r="K16" t="s">
         <v>55</v>
@@ -54867,31 +54867,31 @@
         <v>44287</v>
       </c>
       <c r="B17" t="n">
-        <v>220.937601225894</v>
+        <v>184.577586297597</v>
       </c>
       <c r="C17" t="n">
-        <v>187.001357136517</v>
+        <v>184.616599735439</v>
       </c>
       <c r="D17" t="s">
         <v>40</v>
       </c>
       <c r="E17" t="n">
-        <v>39.7640103886001</v>
+        <v>182.386384187953</v>
       </c>
       <c r="F17" t="n">
-        <v>5.75792040646054</v>
+        <v>181.702130129468</v>
       </c>
       <c r="G17" t="n">
-        <v>443.631863399632</v>
+        <v>186.786234823856</v>
       </c>
       <c r="H17" t="n">
-        <v>652.72372551787</v>
+        <v>187.716289712133</v>
       </c>
       <c r="I17" t="n">
         <v>45</v>
       </c>
       <c r="J17" t="n">
-        <v>142.001357136517</v>
+        <v>139.616599735439</v>
       </c>
       <c r="K17" t="s">
         <v>55</v>
@@ -54902,31 +54902,31 @@
         <v>44317</v>
       </c>
       <c r="B18" t="n">
-        <v>254.109430949008</v>
+        <v>179.805043741077</v>
       </c>
       <c r="C18" t="n">
-        <v>214.759300601918</v>
+        <v>179.735102244902</v>
       </c>
       <c r="D18" t="s">
         <v>40</v>
       </c>
       <c r="E18" t="n">
-        <v>49.3246513603561</v>
+        <v>177.66213902778</v>
       </c>
       <c r="F18" t="n">
-        <v>11.5466446802226</v>
+        <v>176.971664432006</v>
       </c>
       <c r="G18" t="n">
-        <v>501.776855627304</v>
+        <v>181.989612028216</v>
       </c>
       <c r="H18" t="n">
-        <v>730.972808563099</v>
+        <v>182.835483129885</v>
       </c>
       <c r="I18" t="n">
         <v>59</v>
       </c>
       <c r="J18" t="n">
-        <v>155.759300601918</v>
+        <v>120.735102244902</v>
       </c>
       <c r="K18" t="s">
         <v>55</v>
@@ -54937,31 +54937,31 @@
         <v>44348</v>
       </c>
       <c r="B19" t="n">
-        <v>272.877921570479</v>
+        <v>197.850800275235</v>
       </c>
       <c r="C19" t="n">
-        <v>232.327674574404</v>
+        <v>197.788606021812</v>
       </c>
       <c r="D19" t="s">
         <v>40</v>
       </c>
       <c r="E19" t="n">
-        <v>52.192227992357</v>
+        <v>195.572225537747</v>
       </c>
       <c r="F19" t="n">
-        <v>12.2305264476152</v>
+        <v>194.849339595309</v>
       </c>
       <c r="G19" t="n">
-        <v>536.302159682897</v>
+        <v>200.112917878538</v>
       </c>
       <c r="H19" t="n">
-        <v>797.669548253391</v>
+        <v>201.075539122108</v>
       </c>
       <c r="I19" t="n">
         <v>51</v>
       </c>
       <c r="J19" t="n">
-        <v>181.327674574404</v>
+        <v>146.788606021812</v>
       </c>
       <c r="K19" t="s">
         <v>55</v>
@@ -54972,31 +54972,31 @@
         <v>44378</v>
       </c>
       <c r="B20" t="n">
-        <v>290.777209016828</v>
+        <v>211.966544935326</v>
       </c>
       <c r="C20" t="n">
-        <v>247.510712898572</v>
+        <v>211.952880375513</v>
       </c>
       <c r="D20" t="s">
         <v>40</v>
       </c>
       <c r="E20" t="n">
-        <v>57.0262166317119</v>
+        <v>209.579248387854</v>
       </c>
       <c r="F20" t="n">
-        <v>14.4642694651125</v>
+        <v>208.829254159001</v>
       </c>
       <c r="G20" t="n">
-        <v>577.06185240533</v>
+        <v>214.458205386394</v>
       </c>
       <c r="H20" t="n">
-        <v>834.893598540705</v>
+        <v>215.273215566309</v>
       </c>
       <c r="I20" t="n">
         <v>37</v>
       </c>
       <c r="J20" t="n">
-        <v>210.510712898572</v>
+        <v>174.952880375513</v>
       </c>
       <c r="K20" t="s">
         <v>55</v>
@@ -55007,31 +55007,31 @@
         <v>44409</v>
       </c>
       <c r="B21" t="n">
-        <v>270.082763901264</v>
+        <v>207.06276078295</v>
       </c>
       <c r="C21" t="n">
-        <v>227.992041390374</v>
+        <v>207.058316551841</v>
       </c>
       <c r="D21" t="s">
         <v>40</v>
       </c>
       <c r="E21" t="n">
-        <v>44.3519648793245</v>
+        <v>204.748246048917</v>
       </c>
       <c r="F21" t="n">
-        <v>7.02922225884446</v>
+        <v>203.768258558603</v>
       </c>
       <c r="G21" t="n">
-        <v>545.206144526144</v>
+        <v>209.477615553976</v>
       </c>
       <c r="H21" t="n">
-        <v>793.324490849971</v>
+        <v>210.386986156472</v>
       </c>
       <c r="I21" t="n">
         <v>47</v>
       </c>
       <c r="J21" t="n">
-        <v>180.992041390374</v>
+        <v>160.058316551841</v>
       </c>
       <c r="K21" t="s">
         <v>55</v>
@@ -55042,31 +55042,31 @@
         <v>44440</v>
       </c>
       <c r="B22" t="n">
-        <v>251.599522404843</v>
+        <v>197.594289821415</v>
       </c>
       <c r="C22" t="n">
-        <v>204.211252586522</v>
+        <v>197.562821261374</v>
       </c>
       <c r="D22" t="s">
         <v>40</v>
       </c>
       <c r="E22" t="n">
-        <v>35.9092206333153</v>
+        <v>195.349301299142</v>
       </c>
       <c r="F22" t="n">
-        <v>2.91868878603564</v>
+        <v>194.625239248899</v>
       </c>
       <c r="G22" t="n">
-        <v>531.193667737449</v>
+        <v>199.885809960925</v>
       </c>
       <c r="H22" t="n">
-        <v>767.966063479711</v>
+        <v>200.847885466077</v>
       </c>
       <c r="I22" t="n">
         <v>37</v>
       </c>
       <c r="J22" t="n">
-        <v>167.211252586522</v>
+        <v>160.562821261374</v>
       </c>
       <c r="K22" t="s">
         <v>55</v>
@@ -55077,31 +55077,31 @@
         <v>44470</v>
       </c>
       <c r="B23" t="n">
-        <v>228.267616679432</v>
+        <v>174.428670924702</v>
       </c>
       <c r="C23" t="n">
-        <v>177.365251634965</v>
+        <v>174.395578918519</v>
       </c>
       <c r="D23" t="s">
         <v>40</v>
       </c>
       <c r="E23" t="n">
-        <v>23.3333480979935</v>
+        <v>172.30131831606</v>
       </c>
       <c r="F23" t="n">
-        <v>0.318358442876387</v>
+        <v>171.636269228797</v>
       </c>
       <c r="G23" t="n">
-        <v>495.101266267783</v>
+        <v>176.578529421258</v>
       </c>
       <c r="H23" t="n">
-        <v>744.288847063535</v>
+        <v>177.482845935014</v>
       </c>
       <c r="I23" t="n">
         <v>37</v>
       </c>
       <c r="J23" t="n">
-        <v>140.365251634965</v>
+        <v>137.395578918519</v>
       </c>
       <c r="K23" t="s">
         <v>55</v>
@@ -55112,31 +55112,31 @@
         <v>44501</v>
       </c>
       <c r="B24" t="n">
-        <v>197.323820290332</v>
+        <v>155.156838867827</v>
       </c>
       <c r="C24" t="n">
-        <v>147.337868303222</v>
+        <v>155.172181641832</v>
       </c>
       <c r="D24" t="s">
         <v>40</v>
       </c>
       <c r="E24" t="n">
-        <v>11.6790283844367</v>
+        <v>153.142189776927</v>
       </c>
       <c r="F24" t="n">
-        <v>0.01</v>
+        <v>152.501179347498</v>
       </c>
       <c r="G24" t="n">
-        <v>443.889713926705</v>
+        <v>157.31688167504</v>
       </c>
       <c r="H24" t="n">
-        <v>688.125773311493</v>
+        <v>158.015031077059</v>
       </c>
       <c r="I24" t="n">
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>126.337868303222</v>
+        <v>134.172181641832</v>
       </c>
       <c r="K24" t="s">
         <v>55</v>
@@ -55147,31 +55147,31 @@
         <v>44531</v>
       </c>
       <c r="B25" t="n">
-        <v>186.430483543763</v>
+        <v>134.874839538719</v>
       </c>
       <c r="C25" t="n">
-        <v>136.656275924511</v>
+        <v>134.811620913338</v>
       </c>
       <c r="D25" t="s">
         <v>40</v>
       </c>
       <c r="E25" t="n">
-        <v>8.17620724893952</v>
+        <v>133.003985758066</v>
       </c>
       <c r="F25" t="n">
-        <v>0.01</v>
+        <v>132.419755958662</v>
       </c>
       <c r="G25" t="n">
-        <v>428.514802059246</v>
+        <v>136.909755200969</v>
       </c>
       <c r="H25" t="n">
-        <v>663.882904997853</v>
+        <v>137.561102306777</v>
       </c>
       <c r="I25" t="n">
         <v>15</v>
       </c>
       <c r="J25" t="n">
-        <v>121.656275924511</v>
+        <v>119.811620913338</v>
       </c>
       <c r="K25" t="s">
         <v>55</v>
@@ -55182,31 +55182,31 @@
         <v>44562</v>
       </c>
       <c r="B26" t="n">
-        <v>229.006685064614</v>
+        <v>201.997933427499</v>
       </c>
       <c r="C26" t="n">
-        <v>172.651164968418</v>
+        <v>202.011522434233</v>
       </c>
       <c r="D26" t="s">
         <v>40</v>
       </c>
       <c r="E26" t="n">
-        <v>15.2198521605913</v>
+        <v>199.693639275511</v>
       </c>
       <c r="F26" t="n">
-        <v>0.01</v>
+        <v>198.961562920331</v>
       </c>
       <c r="G26" t="n">
-        <v>508.494171978567</v>
+        <v>204.456809036232</v>
       </c>
       <c r="H26" t="n">
-        <v>778.590271524537</v>
+        <v>205.252606299486</v>
       </c>
       <c r="I26" t="n">
         <v>47</v>
       </c>
       <c r="J26" t="n">
-        <v>125.651164968418</v>
+        <v>155.011522434233</v>
       </c>
       <c r="K26" t="s">
         <v>55</v>
@@ -55217,31 +55217,31 @@
         <v>44593</v>
       </c>
       <c r="B27" t="n">
-        <v>243.597398710588</v>
+        <v>213.528128641444</v>
       </c>
       <c r="C27" t="n">
-        <v>183.543789566497</v>
+        <v>213.577010023098</v>
       </c>
       <c r="D27" t="s">
         <v>40</v>
       </c>
       <c r="E27" t="n">
-        <v>16.054156347091</v>
+        <v>211.177727283907</v>
       </c>
       <c r="F27" t="n">
-        <v>0.01</v>
+        <v>210.441394616278</v>
       </c>
       <c r="G27" t="n">
-        <v>544.375327845144</v>
+        <v>215.910142655876</v>
       </c>
       <c r="H27" t="n">
-        <v>843.40768495023</v>
+        <v>216.90999294927</v>
       </c>
       <c r="I27" t="n">
         <v>30</v>
       </c>
       <c r="J27" t="n">
-        <v>153.543789566497</v>
+        <v>183.577010023098</v>
       </c>
       <c r="K27" t="s">
         <v>55</v>
@@ -55252,31 +55252,31 @@
         <v>44621</v>
       </c>
       <c r="B28" t="n">
-        <v>287.288748620757</v>
+        <v>241.15204758671</v>
       </c>
       <c r="C28" t="n">
-        <v>220.711779316135</v>
+        <v>241.164265032809</v>
       </c>
       <c r="D28" t="s">
         <v>40</v>
       </c>
       <c r="E28" t="n">
-        <v>26.0397771734183</v>
+        <v>238.631898067679</v>
       </c>
       <c r="F28" t="n">
-        <v>0.01</v>
+        <v>237.831561810055</v>
       </c>
       <c r="G28" t="n">
-        <v>630.521762282804</v>
+        <v>243.662414861615</v>
       </c>
       <c r="H28" t="n">
-        <v>935.730626893159</v>
+        <v>244.705161460884</v>
       </c>
       <c r="I28" t="n">
         <v>34</v>
       </c>
       <c r="J28" t="n">
-        <v>186.711779316135</v>
+        <v>207.164265032809</v>
       </c>
       <c r="K28" t="s">
         <v>55</v>
@@ -55287,31 +55287,31 @@
         <v>44652</v>
       </c>
       <c r="B29" t="n">
-        <v>250.858489394741</v>
+        <v>184.589680943996</v>
       </c>
       <c r="C29" t="n">
-        <v>182.374740204016</v>
+        <v>184.502281723082</v>
       </c>
       <c r="D29" t="s">
         <v>40</v>
       </c>
       <c r="E29" t="n">
-        <v>11.4207186731178</v>
+        <v>182.40192823251</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01</v>
+        <v>181.702294882847</v>
       </c>
       <c r="G29" t="n">
-        <v>583.752214737601</v>
+        <v>186.786401866268</v>
       </c>
       <c r="H29" t="n">
-        <v>889.502008356859</v>
+        <v>187.716457169901</v>
       </c>
       <c r="I29" t="n">
         <v>35</v>
       </c>
       <c r="J29" t="n">
-        <v>147.374740204016</v>
+        <v>149.502281723082</v>
       </c>
       <c r="K29" t="s">
         <v>55</v>
@@ -55322,31 +55322,31 @@
         <v>44682</v>
       </c>
       <c r="B30" t="n">
-        <v>283.840687282077</v>
+        <v>179.846329303248</v>
       </c>
       <c r="C30" t="n">
-        <v>213.667338407194</v>
+        <v>179.848965943225</v>
       </c>
       <c r="D30" t="s">
         <v>40</v>
       </c>
       <c r="E30" t="n">
-        <v>18.0525845700396</v>
+        <v>177.723086899766</v>
       </c>
       <c r="F30" t="n">
-        <v>0.01</v>
+        <v>176.971824913639</v>
       </c>
       <c r="G30" t="n">
-        <v>630.054971028412</v>
+        <v>182.156636534757</v>
       </c>
       <c r="H30" t="n">
-        <v>1004.60585789235</v>
+        <v>182.907825540253</v>
       </c>
       <c r="I30" t="n">
         <v>41</v>
       </c>
       <c r="J30" t="n">
-        <v>172.667338407194</v>
+        <v>138.848965943225</v>
       </c>
       <c r="K30" t="s">
         <v>55</v>
@@ -55357,31 +55357,31 @@
         <v>44713</v>
       </c>
       <c r="B31" t="n">
-        <v>300.71293995839</v>
+        <v>197.837075114379</v>
       </c>
       <c r="C31" t="n">
-        <v>228.775814501407</v>
+        <v>197.86717324625</v>
       </c>
       <c r="D31" t="s">
         <v>40</v>
       </c>
       <c r="E31" t="n">
-        <v>21.6989073022419</v>
+        <v>195.573994950279</v>
       </c>
       <c r="F31" t="n">
-        <v>0.01</v>
+        <v>194.849516219813</v>
       </c>
       <c r="G31" t="n">
-        <v>663.121602720136</v>
+        <v>200.288068038285</v>
       </c>
       <c r="H31" t="n">
-        <v>1039.82466440206</v>
+        <v>201.075718546344</v>
       </c>
       <c r="I31" t="n">
         <v>52</v>
       </c>
       <c r="J31" t="n">
-        <v>176.775814501407</v>
+        <v>145.86717324625</v>
       </c>
       <c r="K31" t="s">
         <v>55</v>
@@ -55392,31 +55392,31 @@
         <v>44743</v>
       </c>
       <c r="B32" t="n">
-        <v>319.658656465883</v>
+        <v>211.904871776116</v>
       </c>
       <c r="C32" t="n">
-        <v>243.039849431235</v>
+        <v>211.953071031374</v>
       </c>
       <c r="D32" t="s">
         <v>40</v>
       </c>
       <c r="E32" t="n">
-        <v>23.5079397971423</v>
+        <v>209.579437973146</v>
       </c>
       <c r="F32" t="n">
-        <v>0.01</v>
+        <v>208.829443404766</v>
       </c>
       <c r="G32" t="n">
-        <v>707.428377929531</v>
+        <v>214.259202005964</v>
       </c>
       <c r="H32" t="n">
-        <v>1102.47841858203</v>
+        <v>215.195101713714</v>
       </c>
       <c r="I32" t="n">
         <v>56</v>
       </c>
       <c r="J32" t="n">
-        <v>187.039849431235</v>
+        <v>155.953071031374</v>
       </c>
       <c r="K32" t="s">
         <v>55</v>
@@ -55427,31 +55427,31 @@
         <v>44774</v>
       </c>
       <c r="B33" t="n">
-        <v>299.35516858679</v>
+        <v>207.153908879032</v>
       </c>
       <c r="C33" t="n">
-        <v>224.814870572758</v>
+        <v>207.179782247588</v>
       </c>
       <c r="D33" t="s">
         <v>40</v>
       </c>
       <c r="E33" t="n">
-        <v>15.1753281372873</v>
+        <v>204.816807551545</v>
       </c>
       <c r="F33" t="n">
-        <v>0.01</v>
+        <v>204.091659031289</v>
       </c>
       <c r="G33" t="n">
-        <v>685.277427885948</v>
+        <v>209.47780294744</v>
       </c>
       <c r="H33" t="n">
-        <v>1047.17879833794</v>
+        <v>210.462664321015</v>
       </c>
       <c r="I33" t="n">
         <v>61</v>
       </c>
       <c r="J33" t="n">
-        <v>163.814870572758</v>
+        <v>146.179782247588</v>
       </c>
       <c r="K33" t="s">
         <v>55</v>
@@ -55462,31 +55462,31 @@
         <v>44805</v>
       </c>
       <c r="B34" t="n">
-        <v>280.843098868837</v>
+        <v>197.630124155136</v>
       </c>
       <c r="C34" t="n">
-        <v>203.644951041569</v>
+        <v>197.641713742929</v>
       </c>
       <c r="D34" t="s">
         <v>40</v>
       </c>
       <c r="E34" t="n">
-        <v>10.9756501773462</v>
+        <v>195.349478049177</v>
       </c>
       <c r="F34" t="n">
-        <v>0.01</v>
+        <v>194.625415671067</v>
       </c>
       <c r="G34" t="n">
-        <v>656.036253079503</v>
+        <v>199.885988751473</v>
       </c>
       <c r="H34" t="n">
-        <v>1018.52879848442</v>
+        <v>200.84806468638</v>
       </c>
       <c r="I34" t="n">
         <v>65</v>
       </c>
       <c r="J34" t="n">
-        <v>138.644951041569</v>
+        <v>132.641713742929</v>
       </c>
       <c r="K34" t="s">
         <v>55</v>
@@ -55497,31 +55497,31 @@
         <v>44835</v>
       </c>
       <c r="B35" t="n">
-        <v>257.265750688646</v>
+        <v>174.452072043887</v>
       </c>
       <c r="C35" t="n">
-        <v>176.463440747857</v>
+        <v>174.469344084558</v>
       </c>
       <c r="D35" t="s">
         <v>40</v>
       </c>
       <c r="E35" t="n">
-        <v>4.23028666468575</v>
+        <v>172.301474280682</v>
       </c>
       <c r="F35" t="n">
-        <v>0.01</v>
+        <v>171.636424892132</v>
       </c>
       <c r="G35" t="n">
-        <v>620.688051697364</v>
+        <v>176.578687309847</v>
       </c>
       <c r="H35" t="n">
-        <v>975.723576518832</v>
+        <v>177.483004227386</v>
       </c>
       <c r="I35" t="n">
         <v>47</v>
       </c>
       <c r="J35" t="n">
-        <v>129.463440747857</v>
+        <v>127.469344084558</v>
       </c>
       <c r="K35" t="s">
         <v>55</v>
@@ -55532,31 +55532,31 @@
         <v>44866</v>
       </c>
       <c r="B36" t="n">
-        <v>224.90432463097</v>
+        <v>155.144442463669</v>
       </c>
       <c r="C36" t="n">
-        <v>142.152267439018</v>
+        <v>155.102903351155</v>
       </c>
       <c r="D36" t="s">
         <v>40</v>
       </c>
       <c r="E36" t="n">
-        <v>0.440369790964005</v>
+        <v>153.142328447507</v>
       </c>
       <c r="F36" t="n">
-        <v>0.01</v>
+        <v>152.501317727555</v>
       </c>
       <c r="G36" t="n">
-        <v>558.425615422246</v>
+        <v>157.317022223006</v>
       </c>
       <c r="H36" t="n">
-        <v>894.430142203958</v>
+        <v>158.015171936546</v>
       </c>
       <c r="I36" t="n">
         <v>45</v>
       </c>
       <c r="J36" t="n">
-        <v>97.1522674390177</v>
+        <v>110.102903351155</v>
       </c>
       <c r="K36" t="s">
         <v>55</v>
@@ -55567,31 +55567,31 @@
         <v>44896</v>
       </c>
       <c r="B37" t="n">
-        <v>214.194271136395</v>
+        <v>134.878205630036</v>
       </c>
       <c r="C37" t="n">
-        <v>132.543556500772</v>
+        <v>134.909605458851</v>
       </c>
       <c r="D37" t="s">
         <v>40</v>
       </c>
       <c r="E37" t="n">
-        <v>0.01</v>
+        <v>133.017239299382</v>
       </c>
       <c r="F37" t="n">
-        <v>0.01</v>
+        <v>132.419876195405</v>
       </c>
       <c r="G37" t="n">
-        <v>540.067796426657</v>
+        <v>136.765221457929</v>
       </c>
       <c r="H37" t="n">
-        <v>881.520179738333</v>
+        <v>137.561224855457</v>
       </c>
       <c r="I37" t="n">
         <v>36</v>
       </c>
       <c r="J37" t="n">
-        <v>96.5435565007718</v>
+        <v>98.9096054588505</v>
       </c>
       <c r="K37" t="s">
         <v>55</v>
@@ -55602,31 +55602,31 @@
         <v>44927</v>
       </c>
       <c r="B38" t="n">
-        <v>257.43714646739</v>
+        <v>201.979646896471</v>
       </c>
       <c r="C38" t="n">
-        <v>170.418569867081</v>
+        <v>202.010955586244</v>
       </c>
       <c r="D38" t="s">
         <v>40</v>
       </c>
       <c r="E38" t="n">
-        <v>1.88338931168551</v>
+        <v>199.693819944236</v>
       </c>
       <c r="F38" t="n">
-        <v>0.01</v>
+        <v>198.961743257586</v>
       </c>
       <c r="G38" t="n">
-        <v>638.825785783873</v>
+        <v>204.280208683211</v>
       </c>
       <c r="H38" t="n">
-        <v>992.675102003998</v>
+        <v>205.252789465629</v>
       </c>
       <c r="I38" t="n">
         <v>55</v>
       </c>
       <c r="J38" t="n">
-        <v>115.418569867081</v>
+        <v>147.010955586244</v>
       </c>
       <c r="K38" t="s">
         <v>55</v>
@@ -55637,31 +55637,31 @@
         <v>44958</v>
       </c>
       <c r="B39" t="n">
-        <v>271.50202430972</v>
+        <v>213.587260794218</v>
       </c>
       <c r="C39" t="n">
-        <v>182.14137646567</v>
+        <v>213.577202139706</v>
       </c>
       <c r="D39" t="s">
         <v>40</v>
       </c>
       <c r="E39" t="n">
-        <v>2.72328403459646</v>
+        <v>211.268019857844</v>
       </c>
       <c r="F39" t="n">
-        <v>0.01</v>
+        <v>210.548016133856</v>
       </c>
       <c r="G39" t="n">
-        <v>667.986073702294</v>
+        <v>216.092080582774</v>
       </c>
       <c r="H39" t="n">
-        <v>1039.50592096143</v>
+        <v>216.910186559115</v>
       </c>
       <c r="I39" t="n">
         <v>52</v>
       </c>
       <c r="J39" t="n">
-        <v>130.14137646567</v>
+        <v>161.577202139706</v>
       </c>
       <c r="K39" t="s">
         <v>55</v>
@@ -55672,31 +55672,31 @@
         <v>44986</v>
       </c>
       <c r="B40" t="n">
-        <v>316.585357103246</v>
+        <v>241.163585513052</v>
       </c>
       <c r="C40" t="n">
-        <v>219.049470628247</v>
+        <v>241.164481961355</v>
       </c>
       <c r="D40" t="s">
         <v>40</v>
       </c>
       <c r="E40" t="n">
-        <v>8.63185833574447</v>
+        <v>238.632113854281</v>
       </c>
       <c r="F40" t="n">
-        <v>0.01</v>
+        <v>237.831777234495</v>
       </c>
       <c r="G40" t="n">
-        <v>754.951217921937</v>
+        <v>243.836388828457</v>
       </c>
       <c r="H40" t="n">
-        <v>1172.998728107</v>
+        <v>244.705379976154</v>
       </c>
       <c r="I40" t="n">
         <v>51</v>
       </c>
       <c r="J40" t="n">
-        <v>168.049470628247</v>
+        <v>190.164481961355</v>
       </c>
       <c r="K40" t="s">
         <v>55</v>
@@ -55707,31 +55707,31 @@
         <v>45017</v>
       </c>
       <c r="B41" t="n">
-        <v>279.87624030052</v>
+        <v>184.560490492092</v>
       </c>
       <c r="C41" t="n">
-        <v>177.393825844407</v>
+        <v>184.502447741161</v>
       </c>
       <c r="D41" t="s">
         <v>40</v>
       </c>
       <c r="E41" t="n">
-        <v>1.15966970630049</v>
+        <v>182.386714314703</v>
       </c>
       <c r="F41" t="n">
-        <v>0.01</v>
+        <v>181.702459636373</v>
       </c>
       <c r="G41" t="n">
-        <v>698.07378265771</v>
+        <v>186.955614900427</v>
       </c>
       <c r="H41" t="n">
-        <v>1103.01547449631</v>
+        <v>187.716624627818</v>
       </c>
       <c r="I41" t="n">
         <v>56</v>
       </c>
       <c r="J41" t="n">
-        <v>121.393825844407</v>
+        <v>128.502447741161</v>
       </c>
       <c r="K41" t="s">
         <v>55</v>
@@ -55742,31 +55742,31 @@
         <v>45047</v>
       </c>
       <c r="B42" t="n">
-        <v>314.221950513929</v>
+        <v>179.819964223494</v>
       </c>
       <c r="C42" t="n">
-        <v>210.050287853905</v>
+        <v>179.848421416831</v>
       </c>
       <c r="D42" t="s">
         <v>40</v>
       </c>
       <c r="E42" t="n">
-        <v>4.62035566367554</v>
+        <v>177.66246061672</v>
       </c>
       <c r="F42" t="n">
-        <v>0.01</v>
+        <v>176.971985395418</v>
       </c>
       <c r="G42" t="n">
-        <v>751.973939678658</v>
+        <v>181.989937510203</v>
       </c>
       <c r="H42" t="n">
-        <v>1199.08427641912</v>
+        <v>182.907988691278</v>
       </c>
       <c r="I42" t="n">
         <v>53</v>
       </c>
       <c r="J42" t="n">
-        <v>157.050287853905</v>
+        <v>126.848421416831</v>
       </c>
       <c r="K42" t="s">
         <v>55</v>
@@ -55777,31 +55777,31 @@
         <v>45078</v>
       </c>
       <c r="B43" t="n">
-        <v>330.214218308607</v>
+        <v>197.818967403252</v>
       </c>
       <c r="C43" t="n">
-        <v>229.118835358097</v>
+        <v>197.867351233362</v>
       </c>
       <c r="D43" t="s">
         <v>40</v>
       </c>
       <c r="E43" t="n">
-        <v>5.04491058297535</v>
+        <v>195.574171902996</v>
       </c>
       <c r="F43" t="n">
-        <v>0.01</v>
+        <v>194.849692844476</v>
       </c>
       <c r="G43" t="n">
-        <v>776.662317607009</v>
+        <v>200.113275867171</v>
       </c>
       <c r="H43" t="n">
-        <v>1245.92572556804</v>
+        <v>201.07589797074</v>
       </c>
       <c r="I43" t="n">
         <v>59</v>
       </c>
       <c r="J43" t="n">
-        <v>170.118835358097</v>
+        <v>138.867351233362</v>
       </c>
       <c r="K43" t="s">
         <v>55</v>
@@ -55812,31 +55812,31 @@
         <v>45108</v>
       </c>
       <c r="B44" t="n">
-        <v>351.102467635119</v>
+        <v>211.992918564298</v>
       </c>
       <c r="C44" t="n">
-        <v>248.824529010317</v>
+        <v>211.954028449235</v>
       </c>
       <c r="D44" t="s">
         <v>40</v>
       </c>
       <c r="E44" t="n">
-        <v>7.26230912166398</v>
+        <v>209.645649031961</v>
       </c>
       <c r="F44" t="n">
-        <v>0.01</v>
+        <v>208.829632650702</v>
       </c>
       <c r="G44" t="n">
-        <v>826.129940690758</v>
+        <v>214.458588945258</v>
       </c>
       <c r="H44" t="n">
-        <v>1324.80772741892</v>
+        <v>215.966804991102</v>
       </c>
       <c r="I44" t="n">
         <v>50</v>
       </c>
       <c r="J44" t="n">
-        <v>198.824529010317</v>
+        <v>161.954028449235</v>
       </c>
       <c r="K44" t="s">
         <v>55</v>
@@ -55847,31 +55847,31 @@
         <v>45139</v>
       </c>
       <c r="B45" t="n">
-        <v>331.622298669885</v>
+        <v>207.156917974389</v>
       </c>
       <c r="C45" t="n">
-        <v>226.342096808342</v>
+        <v>207.17996861051</v>
       </c>
       <c r="D45" t="s">
         <v>40</v>
       </c>
       <c r="E45" t="n">
-        <v>2.8873337821149</v>
+        <v>204.898559731947</v>
       </c>
       <c r="F45" t="n">
-        <v>0.01</v>
+        <v>204.091844000077</v>
       </c>
       <c r="G45" t="n">
-        <v>803.5104644494</v>
+        <v>209.460055780495</v>
       </c>
       <c r="H45" t="n">
-        <v>1277.03586254665</v>
+        <v>210.385426104945</v>
       </c>
       <c r="I45" t="n">
         <v>64</v>
       </c>
       <c r="J45" t="n">
-        <v>162.342096808342</v>
+        <v>143.17996861051</v>
       </c>
       <c r="K45" t="s">
         <v>55</v>
@@ -55882,31 +55882,31 @@
         <v>45170</v>
       </c>
       <c r="B46" t="n">
-        <v>313.978812570262</v>
+        <v>197.627297474479</v>
       </c>
       <c r="C46" t="n">
-        <v>203.433923597203</v>
+        <v>197.563176758732</v>
       </c>
       <c r="D46" t="s">
         <v>40</v>
       </c>
       <c r="E46" t="n">
-        <v>0.706923831204573</v>
+        <v>195.333739328658</v>
       </c>
       <c r="F46" t="n">
-        <v>0.01</v>
+        <v>194.625592093395</v>
       </c>
       <c r="G46" t="n">
-        <v>787.515463648642</v>
+        <v>200.061039492112</v>
       </c>
       <c r="H46" t="n">
-        <v>1262.38762424454</v>
+        <v>200.848243906843</v>
       </c>
       <c r="I46" t="n">
         <v>49</v>
       </c>
       <c r="J46" t="n">
-        <v>154.433923597203</v>
+        <v>148.563176758732</v>
       </c>
       <c r="K46" t="s">
         <v>55</v>
@@ -55917,31 +55917,31 @@
         <v>45200</v>
       </c>
       <c r="B47" t="n">
-        <v>291.033265403014</v>
+        <v>174.468211820105</v>
       </c>
       <c r="C47" t="n">
-        <v>179.214109578255</v>
+        <v>174.469501027415</v>
       </c>
       <c r="D47" t="s">
         <v>40</v>
       </c>
       <c r="E47" t="n">
-        <v>0.01</v>
+        <v>172.316578005634</v>
       </c>
       <c r="F47" t="n">
-        <v>0.01</v>
+        <v>171.636580555607</v>
       </c>
       <c r="G47" t="n">
-        <v>737.866455100772</v>
+        <v>176.743208247993</v>
       </c>
       <c r="H47" t="n">
-        <v>1174.5082738959</v>
+        <v>177.4831625199</v>
       </c>
       <c r="I47" t="n">
         <v>59</v>
       </c>
       <c r="J47" t="n">
-        <v>120.214109578255</v>
+        <v>115.469501027415</v>
       </c>
       <c r="K47" t="s">
         <v>55</v>
@@ -55952,31 +55952,31 @@
         <v>45231</v>
       </c>
       <c r="B48" t="n">
-        <v>259.969760038467</v>
+        <v>155.149514081652</v>
       </c>
       <c r="C48" t="n">
-        <v>150.684503151041</v>
+        <v>155.172460815226</v>
       </c>
       <c r="D48" t="s">
         <v>40</v>
       </c>
       <c r="E48" t="n">
-        <v>0.01</v>
+        <v>153.128375533414</v>
       </c>
       <c r="F48" t="n">
-        <v>0.01</v>
+        <v>152.501456107737</v>
       </c>
       <c r="G48" t="n">
-        <v>689.841874121285</v>
+        <v>157.162097400905</v>
       </c>
       <c r="H48" t="n">
-        <v>1125.11451128208</v>
+        <v>158.015312796159</v>
       </c>
       <c r="I48" t="n">
         <v>59</v>
       </c>
       <c r="J48" t="n">
-        <v>91.6845031510405</v>
+        <v>96.1724608152262</v>
       </c>
       <c r="K48" t="s">
         <v>55</v>
@@ -55987,31 +55987,31 @@
         <v>45261</v>
       </c>
       <c r="B49" t="n">
-        <v>249.249667948476</v>
+        <v>134.890612463069</v>
       </c>
       <c r="C49" t="n">
-        <v>137.825564134453</v>
+        <v>134.909726820772</v>
       </c>
       <c r="D49" t="s">
         <v>40</v>
       </c>
       <c r="E49" t="n">
-        <v>0.01</v>
+        <v>133.017359807131</v>
       </c>
       <c r="F49" t="n">
-        <v>0.01</v>
+        <v>132.419996432258</v>
       </c>
       <c r="G49" t="n">
-        <v>665.624883367856</v>
+        <v>136.765343651637</v>
       </c>
       <c r="H49" t="n">
-        <v>1099.32220020849</v>
+        <v>137.561347404247</v>
       </c>
       <c r="I49" t="n">
         <v>38</v>
       </c>
       <c r="J49" t="n">
-        <v>99.8255641344534</v>
+        <v>96.9097268207725</v>
       </c>
       <c r="K49" t="s">
         <v>55</v>
@@ -56022,31 +56022,31 @@
         <v>45292</v>
       </c>
       <c r="B50" t="n">
-        <v>293.479605202428</v>
+        <v>201.989684932707</v>
       </c>
       <c r="C50" t="n">
-        <v>175.145518372431</v>
+        <v>202.011137300298</v>
       </c>
       <c r="D50" t="s">
         <v>40</v>
       </c>
       <c r="E50" t="n">
-        <v>0.01</v>
+        <v>199.694000613123</v>
       </c>
       <c r="F50" t="n">
-        <v>0.01</v>
+        <v>198.961923595004</v>
       </c>
       <c r="G50" t="n">
-        <v>767.136462625305</v>
+        <v>204.280391415041</v>
       </c>
       <c r="H50" t="n">
-        <v>1228.58105423594</v>
+        <v>205.252972631936</v>
       </c>
       <c r="I50" t="n">
         <v>61</v>
       </c>
       <c r="J50" t="n">
-        <v>114.145518372431</v>
+        <v>141.011137300298</v>
       </c>
       <c r="K50" t="s">
         <v>55</v>
@@ -56057,31 +56057,31 @@
         <v>45323</v>
       </c>
       <c r="B51" t="n">
-        <v>307.993131214997</v>
+        <v>213.511132059963</v>
       </c>
       <c r="C51" t="n">
-        <v>182.135126974981</v>
+        <v>213.454256309022</v>
       </c>
       <c r="D51" t="s">
         <v>40</v>
       </c>
       <c r="E51" t="n">
-        <v>0.01</v>
+        <v>211.194657713227</v>
       </c>
       <c r="F51" t="n">
-        <v>0.01</v>
+        <v>210.441776018691</v>
       </c>
       <c r="G51" t="n">
-        <v>809.336938053192</v>
+        <v>215.892321135437</v>
       </c>
       <c r="H51" t="n">
-        <v>1284.93277510003</v>
+        <v>216.910380169134</v>
       </c>
       <c r="I51" t="n">
         <v>61</v>
       </c>
       <c r="J51" t="n">
-        <v>121.135126974981</v>
+        <v>152.454256309022</v>
       </c>
       <c r="K51" t="s">
         <v>55</v>
@@ -56092,31 +56092,31 @@
         <v>45352</v>
       </c>
       <c r="B52" t="n">
-        <v>354.208928318096</v>
+        <v>241.173566500358</v>
       </c>
       <c r="C52" t="n">
-        <v>223.630350619542</v>
+        <v>241.165516784574</v>
       </c>
       <c r="D52" t="s">
         <v>40</v>
       </c>
       <c r="E52" t="n">
-        <v>0.396944619598174</v>
+        <v>238.632329641077</v>
       </c>
       <c r="F52" t="n">
-        <v>0.01</v>
+        <v>237.831992659129</v>
       </c>
       <c r="G52" t="n">
-        <v>895.181925265945</v>
+        <v>243.836606955585</v>
       </c>
       <c r="H52" t="n">
-        <v>1429.12407522532</v>
+        <v>244.705598491621</v>
       </c>
       <c r="I52" t="n">
         <v>80</v>
       </c>
       <c r="J52" t="n">
-        <v>143.630350619542</v>
+        <v>161.165516784574</v>
       </c>
       <c r="K52" t="s">
         <v>55</v>
@@ -56127,31 +56127,31 @@
         <v>45383</v>
       </c>
       <c r="B53" t="n">
-        <v>315.411779332908</v>
+        <v>184.589193254325</v>
       </c>
       <c r="C53" t="n">
-        <v>185.505159097995</v>
+        <v>184.617097944173</v>
       </c>
       <c r="D53" t="s">
         <v>40</v>
       </c>
       <c r="E53" t="n">
-        <v>0.01</v>
+        <v>182.402258373476</v>
       </c>
       <c r="F53" t="n">
-        <v>0.01</v>
+        <v>181.702624390049</v>
       </c>
       <c r="G53" t="n">
-        <v>836.638723190219</v>
+        <v>186.78673595154</v>
       </c>
       <c r="H53" t="n">
-        <v>1351.48775046162</v>
+        <v>187.716792085886</v>
       </c>
       <c r="I53" t="n">
         <v>62</v>
       </c>
       <c r="J53" t="n">
-        <v>123.505159097995</v>
+        <v>122.617097944173</v>
       </c>
       <c r="K53" t="s">
         <v>55</v>
@@ -56162,31 +56162,31 @@
         <v>45413</v>
       </c>
       <c r="B54" t="n">
-        <v>352.342575693239</v>
+        <v>179.86945737545</v>
       </c>
       <c r="C54" t="n">
-        <v>215.783223744133</v>
+        <v>179.849289505461</v>
       </c>
       <c r="D54" t="s">
         <v>40</v>
       </c>
       <c r="E54" t="n">
-        <v>0.01</v>
+        <v>177.662621411407</v>
       </c>
       <c r="F54" t="n">
-        <v>0.01</v>
+        <v>176.972145877342</v>
       </c>
       <c r="G54" t="n">
-        <v>908.33177268347</v>
+        <v>182.156962166215</v>
       </c>
       <c r="H54" t="n">
-        <v>1466.26940433156</v>
+        <v>182.908151842449</v>
       </c>
       <c r="I54" t="n">
         <v>54</v>
       </c>
       <c r="J54" t="n">
-        <v>161.783223744133</v>
+        <v>125.849289505461</v>
       </c>
       <c r="K54" t="s">
         <v>55</v>
@@ -56197,31 +56197,31 @@
         <v>45444</v>
       </c>
       <c r="B55" t="n">
-        <v>368.856066362809</v>
+        <v>197.842368645175</v>
       </c>
       <c r="C55" t="n">
-        <v>233.421217784596</v>
+        <v>197.867529220633</v>
       </c>
       <c r="D55" t="s">
         <v>40</v>
       </c>
       <c r="E55" t="n">
-        <v>0.0544425912058255</v>
+        <v>195.574348855872</v>
       </c>
       <c r="F55" t="n">
-        <v>0.01</v>
+        <v>194.849869469299</v>
       </c>
       <c r="G55" t="n">
-        <v>931.697010708127</v>
+        <v>200.113454861729</v>
       </c>
       <c r="H55" t="n">
-        <v>1508.56341546203</v>
+        <v>201.076077395298</v>
       </c>
       <c r="I55" t="n">
         <v>62</v>
       </c>
       <c r="J55" t="n">
-        <v>171.421217784596</v>
+        <v>135.867529220633</v>
       </c>
       <c r="K55" t="s">
         <v>55</v>
@@ -56232,31 +56232,31 @@
         <v>45474</v>
       </c>
       <c r="B56" t="n">
-        <v>390.380096448577</v>
+        <v>211.964005241854</v>
       </c>
       <c r="C56" t="n">
-        <v>249.203666382141</v>
+        <v>211.953452343612</v>
       </c>
       <c r="D56" t="s">
         <v>40</v>
       </c>
       <c r="E56" t="n">
-        <v>0.162556313287157</v>
+        <v>209.579817144241</v>
       </c>
       <c r="F56" t="n">
-        <v>0.01</v>
+        <v>208.829821896808</v>
       </c>
       <c r="G56" t="n">
-        <v>988.817570045957</v>
+        <v>214.277724254077</v>
       </c>
       <c r="H56" t="n">
-        <v>1562.89759611692</v>
+        <v>215.273791997062</v>
       </c>
       <c r="I56" t="n">
         <v>62</v>
       </c>
       <c r="J56" t="n">
-        <v>187.203666382141</v>
+        <v>149.953452343612</v>
       </c>
       <c r="K56" t="s">
         <v>55</v>
@@ -56267,31 +56267,31 @@
         <v>45505</v>
       </c>
       <c r="B57" t="n">
-        <v>369.953522844935</v>
+        <v>207.173471721288</v>
       </c>
       <c r="C57" t="n">
-        <v>228.620683446819</v>
+        <v>207.180154973599</v>
       </c>
       <c r="D57" t="s">
         <v>40</v>
       </c>
       <c r="E57" t="n">
-        <v>0.01</v>
+        <v>204.898745066107</v>
       </c>
       <c r="F57" t="n">
-        <v>0.01</v>
+        <v>204.092028969033</v>
       </c>
       <c r="G57" t="n">
-        <v>951.770687182088</v>
+        <v>209.657195436286</v>
       </c>
       <c r="H57" t="n">
-        <v>1505.22632980214</v>
+        <v>210.463039988447</v>
       </c>
       <c r="I57" t="n">
         <v>70</v>
       </c>
       <c r="J57" t="n">
-        <v>158.620683446819</v>
+        <v>137.180154973599</v>
       </c>
       <c r="K57" t="s">
         <v>55</v>
@@ -56302,31 +56302,31 @@
         <v>45536</v>
       </c>
       <c r="B58" t="n">
-        <v>351.612026663283</v>
+        <v>197.626828190269</v>
       </c>
       <c r="C58" t="n">
-        <v>208.992517960854</v>
+        <v>197.56335450765</v>
       </c>
       <c r="D58" t="s">
         <v>40</v>
       </c>
       <c r="E58" t="n">
-        <v>0.01</v>
+        <v>195.349831549724</v>
       </c>
       <c r="F58" t="n">
-        <v>0.01</v>
+        <v>194.625768515883</v>
       </c>
       <c r="G58" t="n">
-        <v>917.014489132805</v>
+        <v>200.061218361172</v>
       </c>
       <c r="H58" t="n">
-        <v>1496.53305306468</v>
+        <v>200.848423127467</v>
       </c>
       <c r="I58" t="n">
         <v>88</v>
       </c>
       <c r="J58" t="n">
-        <v>120.992517960854</v>
+        <v>109.56335450765</v>
       </c>
       <c r="K58" t="s">
         <v>55</v>
@@ -56337,31 +56337,31 @@
         <v>45566</v>
       </c>
       <c r="B59" t="n">
-        <v>325.0322923352</v>
+        <v>174.372667764777</v>
       </c>
       <c r="C59" t="n">
-        <v>184.868873180142</v>
+        <v>174.248724888094</v>
       </c>
       <c r="D59" t="s">
         <v>40</v>
       </c>
       <c r="E59" t="n">
-        <v>0.01</v>
+        <v>172.316733977303</v>
       </c>
       <c r="F59" t="n">
-        <v>0.01</v>
+        <v>171.636736219223</v>
       </c>
       <c r="G59" t="n">
-        <v>858.380253759371</v>
+        <v>176.562537006649</v>
       </c>
       <c r="H59" t="n">
-        <v>1417.17190211818</v>
+        <v>177.483320812556</v>
       </c>
       <c r="I59" t="n">
         <v>74</v>
       </c>
       <c r="J59" t="n">
-        <v>110.868873180142</v>
+        <v>100.248724888094</v>
       </c>
       <c r="K59" t="s">
         <v>55</v>
@@ -56372,31 +56372,31 @@
         <v>45597</v>
       </c>
       <c r="B60" t="n">
-        <v>292.488693908869</v>
+        <v>155.184812754749</v>
       </c>
       <c r="C60" t="n">
-        <v>147.781636962836</v>
+        <v>155.173256468845</v>
       </c>
       <c r="D60" t="s">
         <v>40</v>
       </c>
       <c r="E60" t="n">
-        <v>0.01</v>
+        <v>153.199042864939</v>
       </c>
       <c r="F60" t="n">
-        <v>0.01</v>
+        <v>152.501594488044</v>
       </c>
       <c r="G60" t="n">
-        <v>793.807358296917</v>
+        <v>157.162237879839</v>
       </c>
       <c r="H60" t="n">
-        <v>1345.92791782252</v>
+        <v>158.015453655898</v>
       </c>
       <c r="I60" t="n">
         <v>115</v>
       </c>
       <c r="J60" t="n">
-        <v>32.7816369628361</v>
+        <v>40.1732564688453</v>
       </c>
       <c r="K60" t="s">
         <v>55</v>
@@ -56407,31 +56407,31 @@
         <v>45627</v>
       </c>
       <c r="B61" t="n">
-        <v>281.301897719045</v>
+        <v>134.847307294026</v>
       </c>
       <c r="C61" t="n">
-        <v>135.456048624911</v>
+        <v>134.811984867026</v>
       </c>
       <c r="D61" t="s">
         <v>40</v>
       </c>
       <c r="E61" t="n">
-        <v>0.01</v>
+        <v>133.004347263467</v>
       </c>
       <c r="F61" t="n">
-        <v>0.01</v>
+        <v>132.420116669219</v>
       </c>
       <c r="G61" t="n">
-        <v>776.842212615054</v>
+        <v>136.765465845455</v>
       </c>
       <c r="H61" t="n">
-        <v>1334.22068609738</v>
+        <v>137.561469953146</v>
       </c>
       <c r="I61" t="n">
         <v>87</v>
       </c>
       <c r="J61" t="n">
-        <v>48.4560486249106</v>
+        <v>47.8119848670261</v>
       </c>
       <c r="K61" t="s">
         <v>55</v>
@@ -56442,31 +56442,31 @@
         <v>45658</v>
       </c>
       <c r="B62" t="n">
-        <v>326.395155089632</v>
+        <v>202.006122046542</v>
       </c>
       <c r="C62" t="n">
-        <v>169.354265191719</v>
+        <v>202.012067577407</v>
       </c>
       <c r="D62" t="s">
         <v>40</v>
       </c>
       <c r="E62" t="n">
-        <v>0.01</v>
+        <v>199.694181282173</v>
       </c>
       <c r="F62" t="n">
-        <v>0.01</v>
+        <v>198.962103932584</v>
       </c>
       <c r="G62" t="n">
-        <v>885.443499736081</v>
+        <v>204.457357468873</v>
       </c>
       <c r="H62" t="n">
-        <v>1423.5962052164</v>
+        <v>205.253155798408</v>
       </c>
       <c r="I62" t="n">
         <v>152</v>
       </c>
       <c r="J62" t="n">
-        <v>17.354265191719</v>
+        <v>50.0120675774067</v>
       </c>
       <c r="K62" t="s">
         <v>55</v>
@@ -56477,31 +56477,31 @@
         <v>45689</v>
       </c>
       <c r="B63" t="n">
-        <v>340.716262507561</v>
+        <v>213.51325420339</v>
       </c>
       <c r="C63" t="n">
-        <v>178.297000468592</v>
+        <v>213.454448370585</v>
       </c>
       <c r="D63" t="s">
         <v>40</v>
       </c>
       <c r="E63" t="n">
-        <v>0.01</v>
+        <v>211.194848755516</v>
       </c>
       <c r="F63" t="n">
-        <v>0.01</v>
+        <v>210.441966720156</v>
       </c>
       <c r="G63" t="n">
-        <v>910.442269863973</v>
+        <v>215.892514290745</v>
       </c>
       <c r="H63" t="n">
-        <v>1521.00381918817</v>
+        <v>216.910573779326</v>
       </c>
       <c r="I63" t="n">
         <v>133</v>
       </c>
       <c r="J63" t="n">
-        <v>45.2970004685922</v>
+        <v>80.4544483705852</v>
       </c>
       <c r="K63" t="s">
         <v>55</v>
@@ -56512,31 +56512,31 @@
         <v>45717</v>
       </c>
       <c r="B64" t="n">
-        <v>388.616298458326</v>
+        <v>241.134560564748</v>
       </c>
       <c r="C64" t="n">
-        <v>217.897046146865</v>
+        <v>241.078373031952</v>
       </c>
       <c r="D64" t="s">
         <v>40</v>
       </c>
       <c r="E64" t="n">
-        <v>0.01</v>
+        <v>238.632545428069</v>
       </c>
       <c r="F64" t="n">
-        <v>0.01</v>
+        <v>237.832208083958</v>
       </c>
       <c r="G64" t="n">
-        <v>1018.97234437957</v>
+        <v>243.643762779455</v>
       </c>
       <c r="H64" t="n">
-        <v>1696.46359137388</v>
+        <v>244.705817007283</v>
       </c>
       <c r="I64" t="n">
         <v>158</v>
       </c>
       <c r="J64" t="n">
-        <v>59.8970461468651</v>
+        <v>83.0783730319516</v>
       </c>
       <c r="K64" t="s">
         <v>55</v>
@@ -56547,31 +56547,31 @@
         <v>45748</v>
       </c>
       <c r="B65" t="n">
-        <v>350.074220810691</v>
+        <v>184.588704718108</v>
       </c>
       <c r="C65" t="n">
-        <v>186.785283703132</v>
+        <v>184.61726401405</v>
       </c>
       <c r="D65" t="s">
         <v>40</v>
       </c>
       <c r="E65" t="n">
-        <v>0.01</v>
+        <v>182.402423444183</v>
       </c>
       <c r="F65" t="n">
-        <v>0.01</v>
+        <v>181.702789143873</v>
       </c>
       <c r="G65" t="n">
-        <v>942.594301760611</v>
+        <v>186.786902994401</v>
       </c>
       <c r="H65" t="n">
-        <v>1600.30198159203</v>
+        <v>187.716959544104</v>
       </c>
       <c r="I65" t="n">
         <v>133</v>
       </c>
       <c r="J65" t="n">
-        <v>53.7852837031317</v>
+        <v>51.6172640140501</v>
       </c>
       <c r="K65" t="s">
         <v>55</v>
@@ -56582,31 +56582,31 @@
         <v>45778</v>
       </c>
       <c r="B66" t="n">
-        <v>384.545064692878</v>
+        <v>179.76416870872</v>
       </c>
       <c r="C66" t="n">
-        <v>215.812926428558</v>
+        <v>179.735749164782</v>
       </c>
       <c r="D66" t="s">
         <v>40</v>
       </c>
       <c r="E66" t="n">
-        <v>0.01</v>
+        <v>177.647604331539</v>
       </c>
       <c r="F66" t="n">
-        <v>0.01</v>
+        <v>176.97230635941</v>
       </c>
       <c r="G66" t="n">
-        <v>1011.87255104774</v>
+        <v>181.973546508663</v>
       </c>
       <c r="H66" t="n">
-        <v>1718.66641572465</v>
+        <v>182.836135605498</v>
       </c>
       <c r="I66" t="n">
         <v>179</v>
       </c>
       <c r="J66" t="n">
-        <v>36.8129264285583</v>
+        <v>0.735749164781765</v>
       </c>
       <c r="K66" t="s">
         <v>55</v>
@@ -56617,31 +56617,31 @@
         <v>45809</v>
       </c>
       <c r="B67" t="n">
-        <v>401.857674082218</v>
+        <v>197.822020259471</v>
       </c>
       <c r="C67" t="n">
-        <v>232.244990237319</v>
+        <v>197.789317829538</v>
       </c>
       <c r="D67" t="s">
         <v>40</v>
       </c>
       <c r="E67" t="n">
-        <v>0.01</v>
+        <v>195.574525808908</v>
       </c>
       <c r="F67" t="n">
-        <v>0.01</v>
+        <v>194.850046094281</v>
       </c>
       <c r="G67" t="n">
-        <v>1065.05420200961</v>
+        <v>200.096104754571</v>
       </c>
       <c r="H67" t="n">
-        <v>1728.07536024039</v>
+        <v>201.000577216115</v>
       </c>
       <c r="I67" t="n">
         <v>160</v>
       </c>
       <c r="J67" t="n">
-        <v>72.2449902373191</v>
+        <v>37.7893178295375</v>
       </c>
       <c r="K67" t="s">
         <v>55</v>
@@ -56652,31 +56652,31 @@
         <v>45839</v>
       </c>
       <c r="B68" t="n">
-        <v>423.020019233326</v>
+        <v>211.905888305048</v>
       </c>
       <c r="C68" t="n">
-        <v>248.24829782261</v>
+        <v>211.953642999988</v>
       </c>
       <c r="D68" t="s">
         <v>40</v>
       </c>
       <c r="E68" t="n">
-        <v>0.01</v>
+        <v>209.580006730045</v>
       </c>
       <c r="F68" t="n">
-        <v>0.01</v>
+        <v>208.830011143086</v>
       </c>
       <c r="G68" t="n">
-        <v>1091.60380568756</v>
+        <v>214.259777077777</v>
       </c>
       <c r="H68" t="n">
-        <v>1813.38193453102</v>
+        <v>215.195678040134</v>
       </c>
       <c r="I68" t="n">
         <v>200</v>
       </c>
       <c r="J68" t="n">
-        <v>48.2482978226097</v>
+        <v>11.9536429999878</v>
       </c>
       <c r="K68" t="s">
         <v>55</v>
@@ -56687,31 +56687,31 @@
         <v>45870</v>
       </c>
       <c r="B69" t="n">
-        <v>402.554537584166</v>
+        <v>207.139420500372</v>
       </c>
       <c r="C69" t="n">
-        <v>225.758717501619</v>
+        <v>207.059061785643</v>
       </c>
       <c r="D69" t="s">
         <v>40</v>
       </c>
       <c r="E69" t="n">
-        <v>0.01</v>
+        <v>204.898930400433</v>
       </c>
       <c r="F69" t="n">
-        <v>0.01</v>
+        <v>204.092213938156</v>
       </c>
       <c r="G69" t="n">
-        <v>1062.60845419656</v>
+        <v>209.47836512884</v>
       </c>
       <c r="H69" t="n">
-        <v>1752.90090821757</v>
+        <v>210.463227822415</v>
       </c>
       <c r="I69" t="n">
         <v>197</v>
       </c>
       <c r="J69" t="n">
-        <v>28.7587175016187</v>
+        <v>10.0590617856427</v>
       </c>
       <c r="K69" t="s">
         <v>55</v>
@@ -56722,31 +56722,31 @@
         <v>45901</v>
       </c>
       <c r="B70" t="n">
-        <v>383.849095996488</v>
+        <v>197.615041843716</v>
       </c>
       <c r="C70" t="n">
-        <v>206.617128743526</v>
+        <v>197.563532256729</v>
       </c>
       <c r="D70" t="s">
         <v>40</v>
       </c>
       <c r="E70" t="n">
-        <v>0.01</v>
+        <v>195.350008300237</v>
       </c>
       <c r="F70" t="n">
-        <v>0.01</v>
+        <v>194.625944938529</v>
       </c>
       <c r="G70" t="n">
-        <v>1026.55093571547</v>
+        <v>199.886525124082</v>
       </c>
       <c r="H70" t="n">
-        <v>1734.37624986541</v>
+        <v>200.848602348252</v>
       </c>
       <c r="I70" t="n">
         <v>262</v>
       </c>
       <c r="J70" t="n">
-        <v>-55.3828712564744</v>
+        <v>-64.4364677432714</v>
       </c>
       <c r="K70" t="s">
         <v>54</v>
@@ -56757,31 +56757,31 @@
         <v>45931</v>
       </c>
       <c r="B71" t="n">
-        <v>357.014851877188</v>
+        <v>174.45664438471</v>
       </c>
       <c r="C71" t="n">
-        <v>185.027542211268</v>
+        <v>174.396206557789</v>
       </c>
       <c r="D71" t="s">
         <v>40</v>
       </c>
       <c r="E71" t="n">
-        <v>0.01</v>
+        <v>172.301942175392</v>
       </c>
       <c r="F71" t="n">
-        <v>0.01</v>
+        <v>171.636891882979</v>
       </c>
       <c r="G71" t="n">
-        <v>973.205780708415</v>
+        <v>176.74352417281</v>
       </c>
       <c r="H71" t="n">
-        <v>1649.60214416277</v>
+        <v>177.483479105353</v>
       </c>
       <c r="I71" t="n">
         <v>208</v>
       </c>
       <c r="J71" t="n">
-        <v>-22.9724577887317</v>
+        <v>-33.6037934422106</v>
       </c>
       <c r="K71" t="s">
         <v>54</v>
@@ -56792,31 +56792,31 @@
         <v>45962</v>
       </c>
       <c r="B72" t="n">
-        <v>324.003556083228</v>
+        <v>155.135480833604</v>
       </c>
       <c r="C72" t="n">
-        <v>147.659499118101</v>
+        <v>155.067783054557</v>
       </c>
       <c r="D72" t="s">
         <v>40</v>
       </c>
       <c r="E72" t="n">
-        <v>0.01</v>
+        <v>153.128652862438</v>
       </c>
       <c r="F72" t="n">
-        <v>0.01</v>
+        <v>152.501732868476</v>
       </c>
       <c r="G72" t="n">
-        <v>905.897609040585</v>
+        <v>157.162378358898</v>
       </c>
       <c r="H72" t="n">
-        <v>1569.59249325152</v>
+        <v>158.015594515764</v>
       </c>
       <c r="I72" t="n">
         <v>169</v>
       </c>
       <c r="J72" t="n">
-        <v>-21.3405008818991</v>
+        <v>-13.9322169454432</v>
       </c>
       <c r="K72" t="s">
         <v>54</v>
@@ -56827,31 +56827,31 @@
         <v>45992</v>
       </c>
       <c r="B73" t="n">
-        <v>313.223602749473</v>
+        <v>134.917869624658</v>
       </c>
       <c r="C73" t="n">
-        <v>133.242916680287</v>
+        <v>134.910581278851</v>
       </c>
       <c r="D73" t="s">
         <v>40</v>
       </c>
       <c r="E73" t="n">
-        <v>0.01</v>
+        <v>133.017600822956</v>
       </c>
       <c r="F73" t="n">
-        <v>0.01</v>
+        <v>132.420236906289</v>
       </c>
       <c r="G73" t="n">
-        <v>883.778305764362</v>
+        <v>136.910244234441</v>
       </c>
       <c r="H73" t="n">
-        <v>1544.73153781352</v>
+        <v>137.561592502155</v>
       </c>
       <c r="I73" t="n">
         <v>182</v>
       </c>
       <c r="J73" t="n">
-        <v>-48.7570833197125</v>
+        <v>-47.0894187211489</v>
       </c>
       <c r="K73" t="s">
         <v>54</v>
